--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bert_vanhecke\Documents\Soortenbehoud\Turnhouts Vennegebied\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bert_vanhecke\Documents\Soortenbehoud\arpl\data\input\Excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1281,7 +1281,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L322"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1329,7 +1328,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1358,7 +1357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1384,7 +1383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1410,7 +1409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1436,7 +1435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1462,7 +1461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1488,7 +1487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1514,7 +1513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1540,7 +1539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1566,7 +1565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1592,7 +1591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1621,7 +1620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1647,7 +1646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1673,7 +1672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1696,7 +1695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1722,7 +1721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1748,7 +1747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1777,7 +1776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1806,7 +1805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1826,7 +1825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1852,7 +1851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -1881,7 +1880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1907,7 +1906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2915,7 +2914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>16</v>
       </c>
@@ -3335,7 +3334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>44</v>
       </c>
@@ -3364,7 +3363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>44</v>
       </c>
@@ -3393,7 +3392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>44</v>
       </c>
@@ -3422,7 +3421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>44</v>
       </c>
@@ -3451,7 +3450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>44</v>
       </c>
@@ -3480,7 +3479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>44</v>
       </c>
@@ -3509,7 +3508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>190</v>
       </c>
@@ -3535,7 +3534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>44</v>
       </c>
@@ -3564,7 +3563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -3593,7 +3592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -3622,7 +3621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>16</v>
       </c>
@@ -3648,7 +3647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>44</v>
       </c>
@@ -3677,7 +3676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>44</v>
       </c>
@@ -3706,7 +3705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>44</v>
       </c>
@@ -3735,7 +3734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>44</v>
       </c>
@@ -3764,7 +3763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>44</v>
       </c>
@@ -3793,7 +3792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>44</v>
       </c>
@@ -3822,7 +3821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>44</v>
       </c>
@@ -3851,7 +3850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>44</v>
       </c>
@@ -3880,7 +3879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -3909,7 +3908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>44</v>
       </c>
@@ -3939,7 +3938,7 @@
       </c>
       <c r="L95" s="1"/>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>44</v>
       </c>
@@ -3968,7 +3967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>191</v>
       </c>
@@ -3997,7 +3996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>44</v>
       </c>
@@ -4026,7 +4025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>190</v>
       </c>
@@ -4081,7 +4080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>32</v>
       </c>
@@ -4107,7 +4106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -4136,7 +4135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>44</v>
       </c>
@@ -4165,7 +4164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>44</v>
       </c>
@@ -4194,7 +4193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>44</v>
       </c>
@@ -4223,7 +4222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>190</v>
       </c>
@@ -4252,7 +4251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>44</v>
       </c>
@@ -4281,7 +4280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>16</v>
       </c>
@@ -4310,7 +4309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>44</v>
       </c>
@@ -4339,7 +4338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>44</v>
       </c>
@@ -4368,7 +4367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>44</v>
       </c>
@@ -4397,7 +4396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>44</v>
       </c>
@@ -4426,7 +4425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -4452,7 +4451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -4481,7 +4480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>44</v>
       </c>
@@ -4510,7 +4509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>44</v>
       </c>
@@ -4539,7 +4538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>44</v>
       </c>
@@ -4568,7 +4567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>190</v>
       </c>
@@ -4594,7 +4593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>44</v>
       </c>
@@ -4623,7 +4622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>16</v>
       </c>
@@ -4649,7 +4648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>16</v>
       </c>
@@ -4678,7 +4677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>44</v>
       </c>
@@ -4707,7 +4706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>16</v>
       </c>
@@ -4736,7 +4735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>44</v>
       </c>
@@ -4765,7 +4764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>16</v>
       </c>
@@ -4794,7 +4793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>16</v>
       </c>
@@ -4823,7 +4822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>44</v>
       </c>
@@ -4852,7 +4851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>44</v>
       </c>
@@ -4881,7 +4880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>44</v>
       </c>
@@ -4910,7 +4909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>44</v>
       </c>
@@ -4939,7 +4938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>44</v>
       </c>
@@ -4968,7 +4967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>44</v>
       </c>
@@ -4997,7 +4996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>44</v>
       </c>
@@ -5026,7 +5025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>44</v>
       </c>
@@ -5055,7 +5054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>190</v>
       </c>
@@ -5081,7 +5080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>190</v>
       </c>
@@ -5107,7 +5106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>44</v>
       </c>
@@ -5136,7 +5135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>44</v>
       </c>
@@ -5165,7 +5164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>190</v>
       </c>
@@ -5194,7 +5193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>44</v>
       </c>
@@ -5223,7 +5222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>44</v>
       </c>
@@ -5252,7 +5251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>44</v>
       </c>
@@ -5281,7 +5280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>40</v>
       </c>
@@ -5310,7 +5309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -5336,7 +5335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>44</v>
       </c>
@@ -5365,7 +5364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>44</v>
       </c>
@@ -5394,7 +5393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>44</v>
       </c>
@@ -5423,7 +5422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>44</v>
       </c>
@@ -5452,7 +5451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>190</v>
       </c>
@@ -5478,7 +5477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>16</v>
       </c>
@@ -5504,7 +5503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>44</v>
       </c>
@@ -5533,7 +5532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>190</v>
       </c>
@@ -5562,7 +5561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>44</v>
       </c>
@@ -5591,7 +5590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>190</v>
       </c>
@@ -5617,7 +5616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>44</v>
       </c>
@@ -5646,7 +5645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>44</v>
       </c>
@@ -5675,7 +5674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>44</v>
       </c>
@@ -5704,7 +5703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>44</v>
       </c>
@@ -5733,7 +5732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>43</v>
       </c>
@@ -5759,7 +5758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>43</v>
       </c>
@@ -5785,7 +5784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>43</v>
       </c>
@@ -5811,7 +5810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>43</v>
       </c>
@@ -5837,7 +5836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>40</v>
       </c>
@@ -5866,7 +5865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>44</v>
       </c>
@@ -5895,7 +5894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>223</v>
       </c>
@@ -5924,7 +5923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>223</v>
       </c>
@@ -5953,7 +5952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>223</v>
       </c>
@@ -5982,7 +5981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>223</v>
       </c>
@@ -6011,7 +6010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>223</v>
       </c>
@@ -6040,7 +6039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>223</v>
       </c>
@@ -6069,7 +6068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>223</v>
       </c>
@@ -6098,7 +6097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>223</v>
       </c>
@@ -6127,7 +6126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>223</v>
       </c>
@@ -6156,7 +6155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>41</v>
       </c>
@@ -6172,6 +6171,9 @@
       <c r="E174">
         <v>10</v>
       </c>
+      <c r="F174">
+        <v>1500</v>
+      </c>
       <c r="G174" t="s">
         <v>274</v>
       </c>
@@ -6182,7 +6184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>16</v>
       </c>
@@ -6208,7 +6210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>16</v>
       </c>
@@ -6237,7 +6239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>16</v>
       </c>
@@ -6266,7 +6268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>16</v>
       </c>
@@ -6295,7 +6297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>16</v>
       </c>
@@ -6324,7 +6326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>190</v>
       </c>
@@ -6350,7 +6352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>44</v>
       </c>
@@ -6379,7 +6381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>44</v>
       </c>
@@ -6408,7 +6410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -6437,7 +6439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>16</v>
       </c>
@@ -6466,7 +6468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>16</v>
       </c>
@@ -6495,7 +6497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>16</v>
       </c>
@@ -6524,7 +6526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>44</v>
       </c>
@@ -6553,7 +6555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>44</v>
       </c>
@@ -6582,7 +6584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>44</v>
       </c>
@@ -6611,7 +6613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>16</v>
       </c>
@@ -6640,7 +6642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>44</v>
       </c>
@@ -6669,7 +6671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>44</v>
       </c>
@@ -6698,7 +6700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>44</v>
       </c>
@@ -6727,7 +6729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>190</v>
       </c>
@@ -6756,7 +6758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>16</v>
       </c>
@@ -6785,7 +6787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>16</v>
       </c>
@@ -6814,7 +6816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>16</v>
       </c>
@@ -6840,7 +6842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>44</v>
       </c>
@@ -6869,7 +6871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>44</v>
       </c>
@@ -6898,7 +6900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>16</v>
       </c>
@@ -6924,7 +6926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>16</v>
       </c>
@@ -6950,7 +6952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>44</v>
       </c>
@@ -6979,7 +6981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>44</v>
       </c>
@@ -7008,7 +7010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>44</v>
       </c>
@@ -7037,7 +7039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>44</v>
       </c>
@@ -7066,7 +7068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>190</v>
       </c>
@@ -7095,7 +7097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>190</v>
       </c>
@@ -7124,7 +7126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>190</v>
       </c>
@@ -7153,7 +7155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>190</v>
       </c>
@@ -7182,7 +7184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>44</v>
       </c>
@@ -7211,7 +7213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>190</v>
       </c>
@@ -7240,7 +7242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>190</v>
       </c>
@@ -7269,7 +7271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>190</v>
       </c>
@@ -7298,7 +7300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>44</v>
       </c>
@@ -7327,7 +7329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>190</v>
       </c>
@@ -7353,7 +7355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>190</v>
       </c>
@@ -7382,7 +7384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>190</v>
       </c>
@@ -7408,7 +7410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>190</v>
       </c>
@@ -7434,7 +7436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>190</v>
       </c>
@@ -7460,7 +7462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>44</v>
       </c>
@@ -7490,7 +7492,7 @@
       </c>
       <c r="L220" s="1"/>
     </row>
-    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>190</v>
       </c>
@@ -7516,7 +7518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>190</v>
       </c>
@@ -7542,7 +7544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>190</v>
       </c>
@@ -7568,7 +7570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>190</v>
       </c>
@@ -7594,7 +7596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>190</v>
       </c>
@@ -7620,7 +7622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>44</v>
       </c>
@@ -7649,7 +7651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>190</v>
       </c>
@@ -7675,7 +7677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>190</v>
       </c>
@@ -7701,7 +7703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>190</v>
       </c>
@@ -7727,7 +7729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>190</v>
       </c>
@@ -7753,7 +7755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>190</v>
       </c>
@@ -7779,7 +7781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>190</v>
       </c>
@@ -7805,7 +7807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>190</v>
       </c>
@@ -7831,7 +7833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>190</v>
       </c>
@@ -7857,7 +7859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>190</v>
       </c>
@@ -7883,7 +7885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>190</v>
       </c>
@@ -7909,7 +7911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>190</v>
       </c>
@@ -7935,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>190</v>
       </c>
@@ -7961,7 +7963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>190</v>
       </c>
@@ -7987,7 +7989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>190</v>
       </c>
@@ -8013,7 +8015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>44</v>
       </c>
@@ -8042,7 +8044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>190</v>
       </c>
@@ -8068,7 +8070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>190</v>
       </c>
@@ -8094,7 +8096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>190</v>
       </c>
@@ -8120,7 +8122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>190</v>
       </c>
@@ -8146,7 +8148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>190</v>
       </c>
@@ -8172,7 +8174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>190</v>
       </c>
@@ -8198,7 +8200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>190</v>
       </c>
@@ -8224,7 +8226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>190</v>
       </c>
@@ -8250,7 +8252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>190</v>
       </c>
@@ -8276,7 +8278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>44</v>
       </c>
@@ -8305,7 +8307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>190</v>
       </c>
@@ -8331,7 +8333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>190</v>
       </c>
@@ -8357,7 +8359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>190</v>
       </c>
@@ -8383,7 +8385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>190</v>
       </c>
@@ -8409,7 +8411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>190</v>
       </c>
@@ -8435,7 +8437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>190</v>
       </c>
@@ -8461,7 +8463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>190</v>
       </c>
@@ -8487,7 +8489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>190</v>
       </c>
@@ -8513,7 +8515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>44</v>
       </c>
@@ -8542,7 +8544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>190</v>
       </c>
@@ -8568,7 +8570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>190</v>
       </c>
@@ -8594,7 +8596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>190</v>
       </c>
@@ -8620,7 +8622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>44</v>
       </c>
@@ -8649,7 +8651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>190</v>
       </c>
@@ -8675,7 +8677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>190</v>
       </c>
@@ -8701,7 +8703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>190</v>
       </c>
@@ -8727,7 +8729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>190</v>
       </c>
@@ -8753,7 +8755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>190</v>
       </c>
@@ -8779,7 +8781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>44</v>
       </c>
@@ -8808,7 +8810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>190</v>
       </c>
@@ -8834,7 +8836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>190</v>
       </c>
@@ -8860,7 +8862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>190</v>
       </c>
@@ -8886,7 +8888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>190</v>
       </c>
@@ -8912,7 +8914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>190</v>
       </c>
@@ -8938,7 +8940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>190</v>
       </c>
@@ -8964,7 +8966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>190</v>
       </c>
@@ -8990,7 +8992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>190</v>
       </c>
@@ -9016,7 +9018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>190</v>
       </c>
@@ -9042,7 +9044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>190</v>
       </c>
@@ -9068,7 +9070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>190</v>
       </c>
@@ -9094,7 +9096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>190</v>
       </c>
@@ -9120,7 +9122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>190</v>
       </c>
@@ -9146,7 +9148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>190</v>
       </c>
@@ -9172,7 +9174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>190</v>
       </c>
@@ -9198,7 +9200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>190</v>
       </c>
@@ -9224,7 +9226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>190</v>
       </c>
@@ -9250,7 +9252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>190</v>
       </c>
@@ -9276,7 +9278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>190</v>
       </c>
@@ -9302,7 +9304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>190</v>
       </c>
@@ -9328,7 +9330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>190</v>
       </c>
@@ -9354,7 +9356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>44</v>
       </c>
@@ -9383,7 +9385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>190</v>
       </c>
@@ -9409,7 +9411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>190</v>
       </c>
@@ -9435,7 +9437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>190</v>
       </c>
@@ -9461,7 +9463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>190</v>
       </c>
@@ -9487,7 +9489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>44</v>
       </c>
@@ -9516,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>190</v>
       </c>
@@ -9542,7 +9544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>190</v>
       </c>
@@ -9568,7 +9570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>190</v>
       </c>
@@ -9594,7 +9596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>190</v>
       </c>
@@ -9620,7 +9622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>190</v>
       </c>
@@ -9646,7 +9648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>190</v>
       </c>
@@ -9672,7 +9674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>190</v>
       </c>
@@ -9698,7 +9700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>190</v>
       </c>
@@ -9724,7 +9726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>190</v>
       </c>
@@ -9750,7 +9752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>42</v>
       </c>
@@ -9776,7 +9778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>191</v>
       </c>
@@ -9805,7 +9807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>191</v>
       </c>
@@ -9834,7 +9836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>191</v>
       </c>
@@ -9863,7 +9865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>191</v>
       </c>
@@ -9892,7 +9894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>16</v>
       </c>
@@ -9918,7 +9920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>191</v>
       </c>
@@ -9947,7 +9949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>191</v>
       </c>
@@ -9973,7 +9975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>191</v>
       </c>
@@ -9999,7 +10001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>191</v>
       </c>
@@ -10025,7 +10027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>191</v>
       </c>
@@ -10051,7 +10053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>191</v>
       </c>
@@ -10077,7 +10079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>191</v>
       </c>
@@ -10103,7 +10105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>191</v>
       </c>
@@ -10129,7 +10131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>191</v>
       </c>
@@ -10155,7 +10157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>191</v>
       </c>
@@ -10183,11 +10185,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I322">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Libellen"/>
-      </filters>
-    </filterColumn>
     <sortState ref="A26:I100">
       <sortCondition ref="B1:B322"/>
     </sortState>

--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="313">
   <si>
     <t>Soort</t>
   </si>
@@ -963,6 +963,9 @@
   </si>
   <si>
     <t>Turnhouts_Vennegebied</t>
+  </si>
+  <si>
+    <t>geleluzernevlinder</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L322"/>
+  <dimension ref="A1:L323"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
@@ -10183,6 +10186,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>16</v>
+      </c>
+      <c r="B323" t="s">
+        <v>312</v>
+      </c>
+      <c r="C323" t="s">
+        <v>264</v>
+      </c>
+      <c r="D323">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I322">
     <sortState ref="A26:I100">

--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$I$323</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$I$352</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1385,6 +1385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L352"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1432,7 +1433,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1458,7 +1459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1487,7 +1488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1513,7 +1514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1568,7 +1569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1626,7 +1627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1655,7 +1656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1684,7 +1685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1742,7 +1743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>190</v>
       </c>
@@ -1797,7 +1798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>190</v>
       </c>
@@ -1823,7 +1824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>190</v>
       </c>
@@ -1849,7 +1850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1878,7 +1879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>223</v>
       </c>
@@ -1936,7 +1937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1965,7 +1966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1994,7 +1995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -2023,7 +2024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -2075,7 +2076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>191</v>
       </c>
@@ -2104,7 +2105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>190</v>
       </c>
@@ -2133,7 +2134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -2162,7 +2163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2191,7 +2192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2220,7 +2221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2278,7 +2279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -2307,7 +2308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -2336,7 +2337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -2365,7 +2366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>190</v>
       </c>
@@ -2391,7 +2392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>190</v>
       </c>
@@ -2417,7 +2418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -2446,7 +2447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -2475,7 +2476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -2533,7 +2534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -2559,7 +2560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>191</v>
       </c>
@@ -2585,7 +2586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>191</v>
       </c>
@@ -2614,7 +2615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>191</v>
       </c>
@@ -2643,7 +2644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -2701,7 +2702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>44</v>
       </c>
@@ -2730,7 +2731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -2788,7 +2789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>44</v>
       </c>
@@ -2817,7 +2818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -2846,7 +2847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>190</v>
       </c>
@@ -2872,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>44</v>
       </c>
@@ -2901,7 +2902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>16</v>
       </c>
@@ -2930,7 +2931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>191</v>
       </c>
@@ -2959,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>190</v>
       </c>
@@ -2985,7 +2986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>190</v>
       </c>
@@ -3040,7 +3041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>44</v>
       </c>
@@ -3069,7 +3070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>191</v>
       </c>
@@ -3098,7 +3099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>191</v>
       </c>
@@ -3124,7 +3125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>191</v>
       </c>
@@ -3150,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>191</v>
       </c>
@@ -3176,7 +3177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>191</v>
       </c>
@@ -3202,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>191</v>
       </c>
@@ -3228,7 +3229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>44</v>
       </c>
@@ -3283,7 +3284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -3309,7 +3310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -3338,7 +3339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -3367,7 +3368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>190</v>
       </c>
@@ -3396,7 +3397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>190</v>
       </c>
@@ -3422,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>32</v>
       </c>
@@ -3451,7 +3452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>190</v>
       </c>
@@ -3480,7 +3481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>16</v>
       </c>
@@ -3523,7 +3524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>190</v>
       </c>
@@ -3549,7 +3550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -3578,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>44</v>
       </c>
@@ -3607,7 +3608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -3636,7 +3637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -3662,7 +3663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -3688,7 +3689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -3714,7 +3715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -3743,7 +3744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -3769,7 +3770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>44</v>
       </c>
@@ -3798,7 +3799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -3853,7 +3854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -3882,7 +3883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -3908,7 +3909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>21</v>
       </c>
@@ -3937,7 +3938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>21</v>
       </c>
@@ -3966,7 +3967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>190</v>
       </c>
@@ -4021,7 +4022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>190</v>
       </c>
@@ -4048,7 +4049,7 @@
       </c>
       <c r="L95" s="1"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>190</v>
       </c>
@@ -4074,7 +4075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>190</v>
       </c>
@@ -4100,7 +4101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>190</v>
       </c>
@@ -4129,7 +4130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>190</v>
       </c>
@@ -4155,7 +4156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>190</v>
       </c>
@@ -4181,7 +4182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>190</v>
       </c>
@@ -4265,7 +4266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>41</v>
       </c>
@@ -4352,7 +4353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>190</v>
       </c>
@@ -4378,7 +4379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>190</v>
       </c>
@@ -4404,7 +4405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>16</v>
       </c>
@@ -4462,7 +4463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>190</v>
       </c>
@@ -4488,7 +4489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>190</v>
       </c>
@@ -4517,7 +4518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>190</v>
       </c>
@@ -4546,7 +4547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>42</v>
       </c>
@@ -4572,7 +4573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>44</v>
       </c>
@@ -4601,7 +4602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>190</v>
       </c>
@@ -4627,7 +4628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>190</v>
       </c>
@@ -4653,7 +4654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>191</v>
       </c>
@@ -4679,7 +4680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>191</v>
       </c>
@@ -4789,7 +4790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -4815,7 +4816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>16</v>
       </c>
@@ -4844,7 +4845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>16</v>
       </c>
@@ -4873,7 +4874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>16</v>
       </c>
@@ -4931,7 +4932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>44</v>
       </c>
@@ -4960,7 +4961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>25</v>
       </c>
@@ -4989,7 +4990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>25</v>
       </c>
@@ -5018,7 +5019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>25</v>
       </c>
@@ -5073,7 +5074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>16</v>
       </c>
@@ -5099,7 +5100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>190</v>
       </c>
@@ -5125,7 +5126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -5151,7 +5152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -5206,7 +5207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>25</v>
       </c>
@@ -5235,7 +5236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>25</v>
       </c>
@@ -5261,7 +5262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>190</v>
       </c>
@@ -5316,7 +5317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>16</v>
       </c>
@@ -5403,7 +5404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>16</v>
       </c>
@@ -5461,7 +5462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>190</v>
       </c>
@@ -5516,7 +5517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>44</v>
       </c>
@@ -5545,7 +5546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>190</v>
       </c>
@@ -5571,7 +5572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>190</v>
       </c>
@@ -5597,7 +5598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>190</v>
       </c>
@@ -5652,7 +5653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>44</v>
       </c>
@@ -5710,7 +5711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>190</v>
       </c>
@@ -5736,7 +5737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>190</v>
       </c>
@@ -5762,7 +5763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -5788,7 +5789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -5843,7 +5844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>190</v>
       </c>
@@ -5869,7 +5870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>16</v>
       </c>
@@ -5898,7 +5899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>16</v>
       </c>
@@ -5927,7 +5928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>44</v>
       </c>
@@ -5982,7 +5983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>190</v>
       </c>
@@ -6037,7 +6038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>190</v>
       </c>
@@ -6092,7 +6093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>44</v>
       </c>
@@ -6121,7 +6122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>190</v>
       </c>
@@ -6147,7 +6148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>190</v>
       </c>
@@ -6176,7 +6177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>190</v>
       </c>
@@ -6202,7 +6203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>190</v>
       </c>
@@ -6228,7 +6229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>190</v>
       </c>
@@ -6254,7 +6255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>44</v>
       </c>
@@ -6283,7 +6284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>44</v>
       </c>
@@ -6341,7 +6342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>40</v>
       </c>
@@ -6370,7 +6371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>190</v>
       </c>
@@ -6396,7 +6397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>190</v>
       </c>
@@ -6448,7 +6449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>44</v>
       </c>
@@ -6535,7 +6536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>25</v>
       </c>
@@ -6564,7 +6565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>25</v>
       </c>
@@ -6593,7 +6594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>25</v>
       </c>
@@ -6622,7 +6623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>44</v>
       </c>
@@ -6677,7 +6678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>190</v>
       </c>
@@ -6703,7 +6704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>16</v>
       </c>
@@ -6758,7 +6759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>223</v>
       </c>
@@ -6816,7 +6817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>190</v>
       </c>
@@ -6842,7 +6843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>190</v>
       </c>
@@ -6868,7 +6869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>43</v>
       </c>
@@ -6894,7 +6895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>43</v>
       </c>
@@ -6920,7 +6921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>25</v>
       </c>
@@ -6946,7 +6947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>25</v>
       </c>
@@ -6972,7 +6973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>25</v>
       </c>
@@ -6998,7 +6999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>25</v>
       </c>
@@ -7027,7 +7028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>25</v>
       </c>
@@ -7056,7 +7057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>25</v>
       </c>
@@ -7114,7 +7115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>190</v>
       </c>
@@ -7140,7 +7141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>190</v>
       </c>
@@ -7166,7 +7167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>44</v>
       </c>
@@ -7195,7 +7196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>190</v>
       </c>
@@ -7250,7 +7251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>44</v>
       </c>
@@ -7279,7 +7280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>43</v>
       </c>
@@ -7305,7 +7306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -7331,7 +7332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -7357,7 +7358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>44</v>
       </c>
@@ -7386,7 +7387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>190</v>
       </c>
@@ -7412,7 +7413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>44</v>
       </c>
@@ -7441,7 +7442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>190</v>
       </c>
@@ -7467,7 +7468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>190</v>
       </c>
@@ -7494,7 +7495,7 @@
       </c>
       <c r="L220" s="1"/>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>16</v>
       </c>
@@ -7520,7 +7521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>190</v>
       </c>
@@ -7546,7 +7547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>190</v>
       </c>
@@ -7572,7 +7573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>190</v>
       </c>
@@ -7598,7 +7599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>190</v>
       </c>
@@ -7624,7 +7625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>25</v>
       </c>
@@ -7650,7 +7651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>25</v>
       </c>
@@ -7705,7 +7706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>190</v>
       </c>
@@ -7731,7 +7732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>190</v>
       </c>
@@ -7757,7 +7758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>21</v>
       </c>
@@ -7835,7 +7836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>190</v>
       </c>
@@ -7861,7 +7862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>190</v>
       </c>
@@ -7887,7 +7888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -7910,7 +7911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -7936,7 +7937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>223</v>
       </c>
@@ -7965,7 +7966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>44</v>
       </c>
@@ -8023,7 +8024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>25</v>
       </c>
@@ -8107,7 +8108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>190</v>
       </c>
@@ -8133,7 +8134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>190</v>
       </c>
@@ -8159,7 +8160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>223</v>
       </c>
@@ -8188,7 +8189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>16</v>
       </c>
@@ -8214,7 +8215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>25</v>
       </c>
@@ -8243,7 +8244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>25</v>
       </c>
@@ -8272,7 +8273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>25</v>
       </c>
@@ -8301,7 +8302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>190</v>
       </c>
@@ -8327,7 +8328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>190</v>
       </c>
@@ -8356,7 +8357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>44</v>
       </c>
@@ -8385,7 +8386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>190</v>
       </c>
@@ -8411,7 +8412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>190</v>
       </c>
@@ -8437,7 +8438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>190</v>
       </c>
@@ -8463,7 +8464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>190</v>
       </c>
@@ -8489,7 +8490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>190</v>
       </c>
@@ -8515,7 +8516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>190</v>
       </c>
@@ -8541,7 +8542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>190</v>
       </c>
@@ -8570,7 +8571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>16</v>
       </c>
@@ -8596,7 +8597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>190</v>
       </c>
@@ -8622,7 +8623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>190</v>
       </c>
@@ -8677,7 +8678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>25</v>
       </c>
@@ -8703,7 +8704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>25</v>
       </c>
@@ -8758,7 +8759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>16</v>
       </c>
@@ -8842,7 +8843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>223</v>
       </c>
@@ -8871,7 +8872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>16</v>
       </c>
@@ -8900,7 +8901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>191</v>
       </c>
@@ -8926,7 +8927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>190</v>
       </c>
@@ -8952,7 +8953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>25</v>
       </c>
@@ -8981,7 +8982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>25</v>
       </c>
@@ -9010,7 +9011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>25</v>
       </c>
@@ -9039,7 +9040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>25</v>
       </c>
@@ -9068,7 +9069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>21</v>
       </c>
@@ -9094,7 +9095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>190</v>
       </c>
@@ -9120,7 +9121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>190</v>
       </c>
@@ -9146,7 +9147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>21</v>
       </c>
@@ -9172,7 +9173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>21</v>
       </c>
@@ -9227,7 +9228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>18</v>
       </c>
@@ -9253,7 +9254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>25</v>
       </c>
@@ -9282,7 +9283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>25</v>
       </c>
@@ -9311,7 +9312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>25</v>
       </c>
@@ -9340,7 +9341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>18</v>
       </c>
@@ -9369,7 +9370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>44</v>
       </c>
@@ -9456,7 +9457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>190</v>
       </c>
@@ -9511,7 +9512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>190</v>
       </c>
@@ -9537,7 +9538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>191</v>
       </c>
@@ -9566,7 +9567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>44</v>
       </c>
@@ -9595,7 +9596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>44</v>
       </c>
@@ -9624,7 +9625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>223</v>
       </c>
@@ -9682,7 +9683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>190</v>
       </c>
@@ -9708,7 +9709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>190</v>
       </c>
@@ -9734,7 +9735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>190</v>
       </c>
@@ -9815,7 +9816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>190</v>
       </c>
@@ -9899,7 +9900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>44</v>
       </c>
@@ -9928,7 +9929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>190</v>
       </c>
@@ -9954,7 +9955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>190</v>
       </c>
@@ -9980,7 +9981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>190</v>
       </c>
@@ -10006,7 +10007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>223</v>
       </c>
@@ -10035,7 +10036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>44</v>
       </c>
@@ -10064,7 +10065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>43</v>
       </c>
@@ -10090,7 +10091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>16</v>
       </c>
@@ -10116,7 +10117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>223</v>
       </c>
@@ -10145,7 +10146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>190</v>
       </c>
@@ -10171,7 +10172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>190</v>
       </c>
@@ -10197,7 +10198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>190</v>
       </c>
@@ -10223,7 +10224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>190</v>
       </c>
@@ -10249,7 +10250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>190</v>
       </c>
@@ -10275,7 +10276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>223</v>
       </c>
@@ -10304,7 +10305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>342</v>
       </c>
@@ -10312,7 +10313,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>41</v>
       </c>
@@ -10320,7 +10321,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>190</v>
       </c>
@@ -10328,7 +10329,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>342</v>
       </c>
@@ -10336,7 +10337,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>342</v>
       </c>
@@ -10344,7 +10345,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>44</v>
       </c>
@@ -10361,7 +10362,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>342</v>
       </c>
@@ -10369,7 +10370,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>44</v>
       </c>
@@ -10386,7 +10387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>342</v>
       </c>
@@ -10394,7 +10395,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>342</v>
       </c>
@@ -10402,7 +10403,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>342</v>
       </c>
@@ -10410,7 +10411,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>342</v>
       </c>
@@ -10418,7 +10419,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>44</v>
       </c>
@@ -10435,7 +10436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>342</v>
       </c>
@@ -10443,7 +10444,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>44</v>
       </c>
@@ -10460,7 +10461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>44</v>
       </c>
@@ -10477,7 +10478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>342</v>
       </c>
@@ -10485,7 +10486,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>41</v>
       </c>
@@ -10493,7 +10494,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>342</v>
       </c>
@@ -10501,7 +10502,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>342</v>
       </c>
@@ -10509,7 +10510,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>41</v>
       </c>
@@ -10517,7 +10518,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>342</v>
       </c>
@@ -10525,7 +10526,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>342</v>
       </c>
@@ -10533,7 +10534,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>41</v>
       </c>
@@ -10541,7 +10542,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>44</v>
       </c>
@@ -10558,7 +10559,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>342</v>
       </c>
@@ -10566,7 +10567,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>342</v>
       </c>
@@ -10574,7 +10575,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>190</v>
       </c>
@@ -10582,7 +10583,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>25</v>
       </c>
@@ -10591,7 +10592,17 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I323">
+  <autoFilter ref="A1:I352">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Simpel"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="8">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
     <sortState ref="A2:I323">
       <sortCondition ref="B1:B323"/>
     </sortState>

--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -1557,7 +1557,7 @@
         <v>20</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G6" t="s">
         <v>310</v>
@@ -1615,7 +1615,7 @@
         <v>20</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G8" t="s">
         <v>310</v>
@@ -1731,7 +1731,7 @@
         <v>20</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G12" t="s">
         <v>310</v>
@@ -1786,7 +1786,7 @@
         <v>20</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G14" t="s">
         <v>310</v>
@@ -1925,7 +1925,7 @@
         <v>20</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G19" t="s">
         <v>310</v>
@@ -2050,7 +2050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>190</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>20</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G31" t="s">
         <v>310</v>
@@ -2522,7 +2522,7 @@
         <v>20</v>
       </c>
       <c r="F40">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G40" t="s">
         <v>310</v>
@@ -2690,7 +2690,7 @@
         <v>20</v>
       </c>
       <c r="F46">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G46" t="s">
         <v>310</v>
@@ -2777,7 +2777,7 @@
         <v>20</v>
       </c>
       <c r="F49">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G49" t="s">
         <v>310</v>
@@ -2789,7 +2789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>44</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>20</v>
       </c>
       <c r="F50">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G50" t="s">
         <v>274</v>
@@ -3029,7 +3029,7 @@
         <v>20</v>
       </c>
       <c r="F58">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G58" t="s">
         <v>310</v>
@@ -3258,7 +3258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>190</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>20</v>
       </c>
       <c r="F88">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G88" t="s">
         <v>310</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>190</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>20</v>
       </c>
       <c r="F102">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G102" t="s">
         <v>310</v>
@@ -4237,7 +4237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>20</v>
       </c>
       <c r="F105">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G105" t="s">
         <v>310</v>
@@ -4341,7 +4341,7 @@
         <v>20</v>
       </c>
       <c r="F106">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G106" t="s">
         <v>310</v>
@@ -4451,7 +4451,7 @@
         <v>20</v>
       </c>
       <c r="F110">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G110" t="s">
         <v>310</v>
@@ -4706,7 +4706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>16</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>20</v>
       </c>
       <c r="F122">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G122" t="s">
         <v>310</v>
@@ -4920,7 +4920,7 @@
         <v>20</v>
       </c>
       <c r="F127">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G127" t="s">
         <v>310</v>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>190</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -5305,7 +5305,7 @@
         <v>20</v>
       </c>
       <c r="F141">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G141" t="s">
         <v>310</v>
@@ -5363,7 +5363,7 @@
         <v>20</v>
       </c>
       <c r="F143">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G143" t="s">
         <v>310</v>
@@ -5375,7 +5375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>16</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>20</v>
       </c>
       <c r="F146">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G146" t="s">
         <v>310</v>
@@ -5505,7 +5505,7 @@
         <v>20</v>
       </c>
       <c r="F148">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G148" t="s">
         <v>310</v>
@@ -5641,7 +5641,7 @@
         <v>20</v>
       </c>
       <c r="F153">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G153" t="s">
         <v>310</v>
@@ -5699,7 +5699,7 @@
         <v>20</v>
       </c>
       <c r="F155">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G155" t="s">
         <v>310</v>
@@ -5832,7 +5832,7 @@
         <v>20</v>
       </c>
       <c r="F160">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G160" t="s">
         <v>310</v>
@@ -5957,7 +5957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>190</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>20</v>
       </c>
       <c r="F167">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G167" t="s">
         <v>310</v>
@@ -6081,7 +6081,7 @@
         <v>20</v>
       </c>
       <c r="F169">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G169" t="s">
         <v>310</v>
@@ -6330,7 +6330,7 @@
         <v>20</v>
       </c>
       <c r="F178">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G178" t="s">
         <v>310</v>
@@ -6423,7 +6423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>20</v>
       </c>
       <c r="F184">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G184" t="s">
         <v>310</v>
@@ -6524,7 +6524,7 @@
         <v>20</v>
       </c>
       <c r="F185">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G185" t="s">
         <v>310</v>
@@ -6652,7 +6652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>190</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>20</v>
       </c>
       <c r="F193">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G193" t="s">
         <v>310</v>
@@ -6788,7 +6788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>190</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>20</v>
       </c>
       <c r="F206">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G206" t="s">
         <v>310</v>
@@ -7239,7 +7239,7 @@
         <v>20</v>
       </c>
       <c r="F211">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G211" t="s">
         <v>310</v>
@@ -7694,7 +7694,7 @@
         <v>20</v>
       </c>
       <c r="F228">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G228" t="s">
         <v>310</v>
@@ -7795,7 +7795,7 @@
         <v>20</v>
       </c>
       <c r="F232">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G232" t="s">
         <v>310</v>
@@ -7824,7 +7824,7 @@
         <v>20</v>
       </c>
       <c r="F233">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G233" t="s">
         <v>310</v>
@@ -8012,7 +8012,7 @@
         <v>20</v>
       </c>
       <c r="F240">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G240" t="s">
         <v>310</v>
@@ -8067,7 +8067,7 @@
         <v>20</v>
       </c>
       <c r="F242">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G242" t="s">
         <v>310</v>
@@ -8096,7 +8096,7 @@
         <v>20</v>
       </c>
       <c r="F243">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G243" t="s">
         <v>310</v>
@@ -8666,7 +8666,7 @@
         <v>20</v>
       </c>
       <c r="F264">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G264" t="s">
         <v>310</v>
@@ -8747,7 +8747,7 @@
         <v>20</v>
       </c>
       <c r="F267">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G267" t="s">
         <v>310</v>
@@ -8802,7 +8802,7 @@
         <v>20</v>
       </c>
       <c r="F269">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G269" t="s">
         <v>310</v>
@@ -8831,7 +8831,7 @@
         <v>20</v>
       </c>
       <c r="F270">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G270" t="s">
         <v>310</v>
@@ -9216,7 +9216,7 @@
         <v>20</v>
       </c>
       <c r="F284">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G284" t="s">
         <v>310</v>
@@ -9416,7 +9416,7 @@
         <v>20</v>
       </c>
       <c r="F291">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G291" t="s">
         <v>310</v>
@@ -9445,7 +9445,7 @@
         <v>20</v>
       </c>
       <c r="F292">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G292" t="s">
         <v>310</v>
@@ -9500,7 +9500,7 @@
         <v>20</v>
       </c>
       <c r="F294">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G294" t="s">
         <v>310</v>
@@ -9671,7 +9671,7 @@
         <v>20</v>
       </c>
       <c r="F300">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G300" t="s">
         <v>310</v>
@@ -9761,7 +9761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>190</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>20</v>
       </c>
       <c r="F305">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G305" t="s">
         <v>310</v>
@@ -9859,7 +9859,7 @@
         <v>20</v>
       </c>
       <c r="F307">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G307" t="s">
         <v>310</v>
@@ -9888,7 +9888,7 @@
         <v>20</v>
       </c>
       <c r="F308">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G308" t="s">
         <v>310</v>
@@ -10593,9 +10593,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I352">
-    <filterColumn colId="6">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Simpel"/>
+        <filter val="Planten"/>
       </filters>
     </filterColumn>
     <filterColumn colId="8">

--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="343">
   <si>
     <t>Soort</t>
   </si>
@@ -1385,7 +1385,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L352"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1433,7 +1432,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1459,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1488,7 +1487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1514,7 +1513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1569,7 +1568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1627,7 +1626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1656,7 +1655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1685,7 +1684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1743,7 +1742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>190</v>
       </c>
@@ -1798,7 +1797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>190</v>
       </c>
@@ -1824,7 +1823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>190</v>
       </c>
@@ -1850,7 +1849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1879,7 +1878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>223</v>
       </c>
@@ -1937,7 +1936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1966,7 +1965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1995,7 +1994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -2024,7 +2023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -2050,7 +2049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>190</v>
       </c>
@@ -2076,7 +2075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>191</v>
       </c>
@@ -2105,7 +2104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>190</v>
       </c>
@@ -2134,7 +2133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -2163,7 +2162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2192,7 +2191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2221,7 +2220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2279,7 +2278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -2308,7 +2307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -2337,7 +2336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -2366,7 +2365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>190</v>
       </c>
@@ -2392,7 +2391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>190</v>
       </c>
@@ -2418,7 +2417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -2447,7 +2446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -2476,7 +2475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -2534,7 +2533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -2560,7 +2559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>191</v>
       </c>
@@ -2586,7 +2585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>191</v>
       </c>
@@ -2615,7 +2614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>191</v>
       </c>
@@ -2644,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -2702,7 +2701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>44</v>
       </c>
@@ -2731,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -2818,7 +2817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -2847,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>190</v>
       </c>
@@ -2873,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>44</v>
       </c>
@@ -2902,7 +2901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>16</v>
       </c>
@@ -2931,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>191</v>
       </c>
@@ -2960,7 +2959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>190</v>
       </c>
@@ -2986,7 +2985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>190</v>
       </c>
@@ -3041,7 +3040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>44</v>
       </c>
@@ -3070,7 +3069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>191</v>
       </c>
@@ -3099,7 +3098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>191</v>
       </c>
@@ -3125,7 +3124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>191</v>
       </c>
@@ -3151,7 +3150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>191</v>
       </c>
@@ -3177,7 +3176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>191</v>
       </c>
@@ -3203,7 +3202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>191</v>
       </c>
@@ -3229,7 +3228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>44</v>
       </c>
@@ -3258,7 +3257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>190</v>
       </c>
@@ -3284,7 +3283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -3310,7 +3309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -3339,7 +3338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -3368,7 +3367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>190</v>
       </c>
@@ -3397,7 +3396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>190</v>
       </c>
@@ -3423,7 +3422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>32</v>
       </c>
@@ -3452,7 +3451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>190</v>
       </c>
@@ -3481,7 +3480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>16</v>
       </c>
@@ -3494,8 +3493,23 @@
       <c r="D75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E75">
+        <v>50</v>
+      </c>
+      <c r="F75">
+        <v>5000</v>
+      </c>
+      <c r="G75" t="s">
+        <v>310</v>
+      </c>
+      <c r="H75" t="s">
+        <v>291</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -3524,7 +3538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>190</v>
       </c>
@@ -3550,7 +3564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -3579,7 +3593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>44</v>
       </c>
@@ -3608,7 +3622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -3637,7 +3651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -3663,7 +3677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -3689,7 +3703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -3715,7 +3729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -3744,7 +3758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -3770,7 +3784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>44</v>
       </c>
@@ -3799,7 +3813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -3854,7 +3868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -3883,7 +3897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -3909,7 +3923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>21</v>
       </c>
@@ -3938,7 +3952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>21</v>
       </c>
@@ -3967,7 +3981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>190</v>
       </c>
@@ -3993,7 +4007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>190</v>
       </c>
@@ -4022,7 +4036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>190</v>
       </c>
@@ -4049,7 +4063,7 @@
       </c>
       <c r="L95" s="1"/>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>190</v>
       </c>
@@ -4075,7 +4089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>190</v>
       </c>
@@ -4101,7 +4115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>190</v>
       </c>
@@ -4130,7 +4144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>190</v>
       </c>
@@ -4156,7 +4170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>190</v>
       </c>
@@ -4182,7 +4196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>190</v>
       </c>
@@ -4237,7 +4251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -4266,7 +4280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>41</v>
       </c>
@@ -4353,7 +4367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>190</v>
       </c>
@@ -4379,7 +4393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>190</v>
       </c>
@@ -4405,7 +4419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>16</v>
       </c>
@@ -4463,7 +4477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>190</v>
       </c>
@@ -4489,7 +4503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>190</v>
       </c>
@@ -4518,7 +4532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>190</v>
       </c>
@@ -4547,7 +4561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>42</v>
       </c>
@@ -4573,7 +4587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>44</v>
       </c>
@@ -4602,7 +4616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>190</v>
       </c>
@@ -4628,7 +4642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>190</v>
       </c>
@@ -4654,7 +4668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>191</v>
       </c>
@@ -4680,7 +4694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>191</v>
       </c>
@@ -4706,7 +4720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -4732,7 +4746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>16</v>
       </c>
@@ -4790,7 +4804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -4816,7 +4830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>16</v>
       </c>
@@ -4845,7 +4859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>16</v>
       </c>
@@ -4874,7 +4888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>16</v>
       </c>
@@ -4932,7 +4946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>44</v>
       </c>
@@ -4961,7 +4975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>25</v>
       </c>
@@ -4990,7 +5004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>25</v>
       </c>
@@ -5019,7 +5033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>25</v>
       </c>
@@ -5048,7 +5062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>190</v>
       </c>
@@ -5074,7 +5088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>16</v>
       </c>
@@ -5100,7 +5114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>190</v>
       </c>
@@ -5126,7 +5140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -5152,7 +5166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -5178,7 +5192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -5207,7 +5221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>25</v>
       </c>
@@ -5236,7 +5250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>25</v>
       </c>
@@ -5262,7 +5276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>190</v>
       </c>
@@ -5317,7 +5331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>16</v>
       </c>
@@ -5375,7 +5389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>16</v>
       </c>
@@ -5404,7 +5418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>16</v>
       </c>
@@ -5462,7 +5476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>190</v>
       </c>
@@ -5517,7 +5531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>44</v>
       </c>
@@ -5546,7 +5560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>190</v>
       </c>
@@ -5572,7 +5586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>190</v>
       </c>
@@ -5598,7 +5612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>190</v>
       </c>
@@ -5653,7 +5667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>44</v>
       </c>
@@ -5711,7 +5725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>190</v>
       </c>
@@ -5737,7 +5751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>190</v>
       </c>
@@ -5763,7 +5777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -5789,7 +5803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -5844,7 +5858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>190</v>
       </c>
@@ -5870,7 +5884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>16</v>
       </c>
@@ -5899,7 +5913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>16</v>
       </c>
@@ -5928,7 +5942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>44</v>
       </c>
@@ -5957,7 +5971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>190</v>
       </c>
@@ -5983,7 +5997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>190</v>
       </c>
@@ -6038,7 +6052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>190</v>
       </c>
@@ -6093,7 +6107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>44</v>
       </c>
@@ -6122,7 +6136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>190</v>
       </c>
@@ -6148,7 +6162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>190</v>
       </c>
@@ -6177,7 +6191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>190</v>
       </c>
@@ -6203,7 +6217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>190</v>
       </c>
@@ -6229,7 +6243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>190</v>
       </c>
@@ -6255,7 +6269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>44</v>
       </c>
@@ -6284,7 +6298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>44</v>
       </c>
@@ -6342,7 +6356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>40</v>
       </c>
@@ -6371,7 +6385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>190</v>
       </c>
@@ -6397,7 +6411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>190</v>
       </c>
@@ -6423,7 +6437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -6449,7 +6463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>44</v>
       </c>
@@ -6536,7 +6550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>25</v>
       </c>
@@ -6565,7 +6579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>25</v>
       </c>
@@ -6594,7 +6608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>25</v>
       </c>
@@ -6623,7 +6637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>44</v>
       </c>
@@ -6652,7 +6666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>190</v>
       </c>
@@ -6678,7 +6692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>190</v>
       </c>
@@ -6704,7 +6718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>16</v>
       </c>
@@ -6759,7 +6773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>223</v>
       </c>
@@ -6788,7 +6802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>190</v>
       </c>
@@ -6817,7 +6831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>190</v>
       </c>
@@ -6843,7 +6857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>190</v>
       </c>
@@ -6869,7 +6883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>43</v>
       </c>
@@ -6895,7 +6909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>43</v>
       </c>
@@ -6921,7 +6935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>25</v>
       </c>
@@ -6947,7 +6961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>25</v>
       </c>
@@ -6973,7 +6987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>25</v>
       </c>
@@ -6999,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>25</v>
       </c>
@@ -7028,7 +7042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>25</v>
       </c>
@@ -7057,7 +7071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>25</v>
       </c>
@@ -7115,7 +7129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>190</v>
       </c>
@@ -7141,7 +7155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>190</v>
       </c>
@@ -7167,7 +7181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>44</v>
       </c>
@@ -7196,7 +7210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>190</v>
       </c>
@@ -7251,7 +7265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>44</v>
       </c>
@@ -7280,7 +7294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>43</v>
       </c>
@@ -7306,7 +7320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -7332,7 +7346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -7358,7 +7372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>44</v>
       </c>
@@ -7387,7 +7401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>190</v>
       </c>
@@ -7413,7 +7427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>44</v>
       </c>
@@ -7442,7 +7456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>190</v>
       </c>
@@ -7468,7 +7482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>190</v>
       </c>
@@ -7495,7 +7509,7 @@
       </c>
       <c r="L220" s="1"/>
     </row>
-    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>16</v>
       </c>
@@ -7521,7 +7535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>190</v>
       </c>
@@ -7547,7 +7561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>190</v>
       </c>
@@ -7573,7 +7587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>190</v>
       </c>
@@ -7599,7 +7613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>190</v>
       </c>
@@ -7625,7 +7639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>25</v>
       </c>
@@ -7651,7 +7665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>25</v>
       </c>
@@ -7706,7 +7720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>190</v>
       </c>
@@ -7732,7 +7746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>190</v>
       </c>
@@ -7758,7 +7772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>21</v>
       </c>
@@ -7836,7 +7850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>190</v>
       </c>
@@ -7862,7 +7876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>190</v>
       </c>
@@ -7888,7 +7902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -7911,7 +7925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -7937,7 +7951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>223</v>
       </c>
@@ -7966,7 +7980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>44</v>
       </c>
@@ -8024,7 +8038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>25</v>
       </c>
@@ -8108,7 +8122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>190</v>
       </c>
@@ -8134,7 +8148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>190</v>
       </c>
@@ -8160,7 +8174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>223</v>
       </c>
@@ -8189,7 +8203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>16</v>
       </c>
@@ -8215,7 +8229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>25</v>
       </c>
@@ -8244,7 +8258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>25</v>
       </c>
@@ -8273,7 +8287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>25</v>
       </c>
@@ -8302,7 +8316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>190</v>
       </c>
@@ -8328,7 +8342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>190</v>
       </c>
@@ -8357,7 +8371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>44</v>
       </c>
@@ -8386,7 +8400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>190</v>
       </c>
@@ -8412,7 +8426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>190</v>
       </c>
@@ -8438,7 +8452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>190</v>
       </c>
@@ -8464,7 +8478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>190</v>
       </c>
@@ -8490,7 +8504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>190</v>
       </c>
@@ -8516,7 +8530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>190</v>
       </c>
@@ -8542,7 +8556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>190</v>
       </c>
@@ -8571,7 +8585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>16</v>
       </c>
@@ -8597,7 +8611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>190</v>
       </c>
@@ -8623,7 +8637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>190</v>
       </c>
@@ -8678,7 +8692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>25</v>
       </c>
@@ -8704,7 +8718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>25</v>
       </c>
@@ -8759,7 +8773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>16</v>
       </c>
@@ -8843,7 +8857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>223</v>
       </c>
@@ -8872,7 +8886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>16</v>
       </c>
@@ -8901,7 +8915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>191</v>
       </c>
@@ -8927,7 +8941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>190</v>
       </c>
@@ -8953,7 +8967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>25</v>
       </c>
@@ -8982,7 +8996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>25</v>
       </c>
@@ -9011,7 +9025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>25</v>
       </c>
@@ -9040,7 +9054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>25</v>
       </c>
@@ -9069,7 +9083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>21</v>
       </c>
@@ -9095,7 +9109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>190</v>
       </c>
@@ -9121,7 +9135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>190</v>
       </c>
@@ -9147,7 +9161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>21</v>
       </c>
@@ -9173,7 +9187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>21</v>
       </c>
@@ -9228,7 +9242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>18</v>
       </c>
@@ -9254,7 +9268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>25</v>
       </c>
@@ -9283,7 +9297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>25</v>
       </c>
@@ -9312,7 +9326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>25</v>
       </c>
@@ -9341,7 +9355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>18</v>
       </c>
@@ -9370,7 +9384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>44</v>
       </c>
@@ -9457,7 +9471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>190</v>
       </c>
@@ -9512,7 +9526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>190</v>
       </c>
@@ -9538,7 +9552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>191</v>
       </c>
@@ -9567,7 +9581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>44</v>
       </c>
@@ -9596,7 +9610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>44</v>
       </c>
@@ -9625,7 +9639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>223</v>
       </c>
@@ -9683,7 +9697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>190</v>
       </c>
@@ -9709,7 +9723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>190</v>
       </c>
@@ -9735,7 +9749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>190</v>
       </c>
@@ -9761,7 +9775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>190</v>
       </c>
@@ -9816,7 +9830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>190</v>
       </c>
@@ -9900,7 +9914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>44</v>
       </c>
@@ -9929,7 +9943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>190</v>
       </c>
@@ -9955,7 +9969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>190</v>
       </c>
@@ -9981,7 +9995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>190</v>
       </c>
@@ -10007,7 +10021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>223</v>
       </c>
@@ -10036,7 +10050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>44</v>
       </c>
@@ -10065,7 +10079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>43</v>
       </c>
@@ -10091,7 +10105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>16</v>
       </c>
@@ -10117,7 +10131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>223</v>
       </c>
@@ -10146,7 +10160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>190</v>
       </c>
@@ -10172,7 +10186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>190</v>
       </c>
@@ -10198,7 +10212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>190</v>
       </c>
@@ -10224,7 +10238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>190</v>
       </c>
@@ -10250,7 +10264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>190</v>
       </c>
@@ -10276,7 +10290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>223</v>
       </c>
@@ -10305,7 +10319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>342</v>
       </c>
@@ -10313,7 +10327,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>41</v>
       </c>
@@ -10321,7 +10335,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>190</v>
       </c>
@@ -10329,7 +10343,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>342</v>
       </c>
@@ -10337,7 +10351,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>342</v>
       </c>
@@ -10345,7 +10359,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>44</v>
       </c>
@@ -10362,7 +10376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>342</v>
       </c>
@@ -10370,7 +10384,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>44</v>
       </c>
@@ -10387,7 +10401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>342</v>
       </c>
@@ -10395,7 +10409,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>342</v>
       </c>
@@ -10403,7 +10417,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>342</v>
       </c>
@@ -10411,7 +10425,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>342</v>
       </c>
@@ -10419,7 +10433,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>44</v>
       </c>
@@ -10436,7 +10450,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="337" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>342</v>
       </c>
@@ -10444,7 +10458,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="338" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>44</v>
       </c>
@@ -10461,7 +10475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="339" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>44</v>
       </c>
@@ -10478,7 +10492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="340" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>342</v>
       </c>
@@ -10486,7 +10500,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="341" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>41</v>
       </c>
@@ -10494,7 +10508,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="342" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>342</v>
       </c>
@@ -10502,7 +10516,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="343" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>342</v>
       </c>
@@ -10510,7 +10524,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="344" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>41</v>
       </c>
@@ -10518,7 +10532,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="345" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>342</v>
       </c>
@@ -10526,7 +10540,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="346" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>342</v>
       </c>
@@ -10534,7 +10548,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="347" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>41</v>
       </c>
@@ -10542,7 +10556,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="348" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>44</v>
       </c>
@@ -10559,7 +10573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="349" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>342</v>
       </c>
@@ -10567,7 +10581,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="350" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>342</v>
       </c>
@@ -10575,7 +10589,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="351" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>190</v>
       </c>
@@ -10583,7 +10597,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="352" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>25</v>
       </c>
@@ -10593,16 +10607,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I352">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Planten"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="8">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
     <sortState ref="A2:I323">
       <sortCondition ref="B1:B323"/>
     </sortState>

--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>341</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>190</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>190</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>190</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>190</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>191</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>190</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>190</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>341</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>190</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>190</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>191</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>191</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>191</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>44</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>44</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>44</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>16</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>191</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>44</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>44</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>191</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>191</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>191</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>191</v>
       </c>
@@ -3272,6 +3272,9 @@
       <c r="E70">
         <v>100</v>
       </c>
+      <c r="F70">
+        <v>100000</v>
+      </c>
       <c r="G70" t="s">
         <v>273</v>
       </c>
@@ -3282,7 +3285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>191</v>
       </c>
@@ -3297,6 +3300,9 @@
       </c>
       <c r="E71">
         <v>100</v>
+      </c>
+      <c r="F71">
+        <v>100000</v>
       </c>
       <c r="G71" t="s">
         <v>273</v>
@@ -3337,7 +3343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>190</v>
       </c>
@@ -3363,7 +3369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>341</v>
       </c>
@@ -3571,7 +3577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>44</v>
       </c>
@@ -3591,7 +3597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -3620,7 +3626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -3788,7 +3794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -3814,7 +3820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -3840,7 +3846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>341</v>
       </c>
@@ -3851,7 +3857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>341</v>
       </c>
@@ -3973,7 +3979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>44</v>
       </c>
@@ -4355,7 +4361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>341</v>
       </c>
@@ -4366,7 +4372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>44</v>
       </c>
@@ -4395,7 +4401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -4435,7 +4441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>41</v>
       </c>
@@ -4464,7 +4470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>44</v>
       </c>
@@ -4493,7 +4499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>44</v>
       </c>
@@ -4603,7 +4609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>44</v>
       </c>
@@ -4632,7 +4638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>190</v>
       </c>
@@ -4658,7 +4664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>190</v>
       </c>
@@ -4687,7 +4693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>190</v>
       </c>
@@ -4716,7 +4722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>44</v>
       </c>
@@ -4880,7 +4886,7 @@
         <v>270</v>
       </c>
       <c r="D132">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E132">
         <v>100</v>
@@ -4921,7 +4927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>16</v>
       </c>
@@ -4950,7 +4956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>44</v>
       </c>
@@ -5005,7 +5011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -5034,7 +5040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -5063,7 +5069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>16</v>
       </c>
@@ -5092,7 +5098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>44</v>
       </c>
@@ -5150,7 +5156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>25</v>
       </c>
@@ -5179,7 +5185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>25</v>
       </c>
@@ -5208,7 +5214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -5289,7 +5295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>190</v>
       </c>
@@ -5378,7 +5384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>44</v>
       </c>
@@ -5482,7 +5488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>190</v>
       </c>
@@ -5508,7 +5514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>44</v>
       </c>
@@ -5537,7 +5543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>16</v>
       </c>
@@ -5566,7 +5572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>44</v>
       </c>
@@ -5586,7 +5592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>44</v>
       </c>
@@ -5615,7 +5621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>341</v>
       </c>
@@ -5626,7 +5632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>41</v>
       </c>
@@ -5695,7 +5701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>44</v>
       </c>
@@ -5750,7 +5756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>44</v>
       </c>
@@ -5779,7 +5785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>44</v>
       </c>
@@ -5886,7 +5892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>44</v>
       </c>
@@ -5944,7 +5950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>44</v>
       </c>
@@ -6077,7 +6083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>44</v>
       </c>
@@ -6132,7 +6138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>16</v>
       </c>
@@ -6161,7 +6167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>16</v>
       </c>
@@ -6219,7 +6225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>190</v>
       </c>
@@ -6271,7 +6277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>44</v>
       </c>
@@ -6300,7 +6306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>190</v>
       </c>
@@ -6326,7 +6332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>44</v>
       </c>
@@ -6384,7 +6390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>190</v>
       </c>
@@ -6491,7 +6497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>190</v>
       </c>
@@ -6546,7 +6552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>341</v>
       </c>
@@ -6586,7 +6592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>44</v>
       </c>
@@ -6751,7 +6757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>44</v>
       </c>
@@ -6780,7 +6786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>44</v>
       </c>
@@ -6809,7 +6815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>25</v>
       </c>
@@ -6838,7 +6844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>25</v>
       </c>
@@ -6867,7 +6873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>25</v>
       </c>
@@ -6925,7 +6931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>190</v>
       </c>
@@ -6951,7 +6957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>341</v>
       </c>
@@ -6962,7 +6968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>190</v>
       </c>
@@ -7014,7 +7020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>44</v>
       </c>
@@ -7072,7 +7078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>190</v>
       </c>
@@ -7101,7 +7107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>190</v>
       </c>
@@ -7127,7 +7133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>190</v>
       </c>
@@ -7284,7 +7290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>25</v>
       </c>
@@ -7313,7 +7319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>25</v>
       </c>
@@ -7342,7 +7348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>25</v>
       </c>
@@ -7371,7 +7377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>44</v>
       </c>
@@ -7426,7 +7432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>190</v>
       </c>
@@ -7481,7 +7487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>190</v>
       </c>
@@ -7507,7 +7513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>44</v>
       </c>
@@ -7672,7 +7678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>190</v>
       </c>
@@ -7831,7 +7837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>190</v>
       </c>
@@ -7857,7 +7863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>190</v>
       </c>
@@ -7972,7 +7978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>44</v>
       </c>
@@ -8001,7 +8007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>190</v>
       </c>
@@ -8027,7 +8033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>190</v>
       </c>
@@ -8102,7 +8108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>44</v>
       </c>
@@ -8183,7 +8189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>341</v>
       </c>
@@ -8243,7 +8249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>341</v>
       </c>
@@ -8341,7 +8347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>41</v>
       </c>
@@ -8352,7 +8358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>25</v>
       </c>
@@ -8378,7 +8384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>44</v>
       </c>
@@ -8407,7 +8413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>44</v>
       </c>
@@ -8436,7 +8442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>190</v>
       </c>
@@ -8462,7 +8468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>190</v>
       </c>
@@ -8517,7 +8523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>44</v>
       </c>
@@ -8563,7 +8569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>25</v>
       </c>
@@ -8592,7 +8598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>25</v>
       </c>
@@ -8621,7 +8627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>25</v>
       </c>
@@ -8838,7 +8844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>190</v>
       </c>
@@ -8864,7 +8870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>190</v>
       </c>
@@ -8890,7 +8896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>190</v>
       </c>
@@ -8997,7 +9003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>44</v>
       </c>
@@ -9144,7 +9150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>44</v>
       </c>
@@ -9173,7 +9179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>44</v>
       </c>
@@ -9260,7 +9266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>191</v>
       </c>
@@ -9312,7 +9318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>25</v>
       </c>
@@ -9341,7 +9347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>25</v>
       </c>
@@ -9370,7 +9376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>25</v>
       </c>
@@ -9399,7 +9405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>25</v>
       </c>
@@ -9558,7 +9564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>44</v>
       </c>
@@ -9758,7 +9764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>44</v>
       </c>
@@ -9787,7 +9793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>44</v>
       </c>
@@ -9842,7 +9848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>44</v>
       </c>
@@ -9871,7 +9877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>190</v>
       </c>
@@ -9926,7 +9932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>341</v>
       </c>
@@ -10024,7 +10030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>44</v>
       </c>
@@ -10053,7 +10059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>190</v>
       </c>
@@ -10079,7 +10085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>190</v>
       </c>
@@ -10105,7 +10111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>190</v>
       </c>
@@ -10131,7 +10137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>190</v>
       </c>
@@ -10186,7 +10192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>190</v>
       </c>
@@ -10212,7 +10218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>44</v>
       </c>
@@ -10241,7 +10247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>44</v>
       </c>
@@ -10351,7 +10357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>190</v>
       </c>
@@ -10487,7 +10493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>190</v>
       </c>
@@ -10527,7 +10533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>25</v>
       </c>
@@ -10538,7 +10544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>190</v>
       </c>
@@ -10564,7 +10570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>190</v>
       </c>
@@ -10616,7 +10622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>190</v>
       </c>
@@ -10642,7 +10648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>190</v>
       </c>
@@ -10699,9 +10705,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I352">
-    <filterColumn colId="8">
+    <filterColumn colId="0">
       <filters>
-        <filter val="1"/>
+        <filter val="Zoogdieren"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:I352">

--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -1095,17 +1095,7 @@
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1463,7 +1453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1518,7 +1508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1541,10 +1531,10 @@
         <v>289</v>
       </c>
       <c r="I5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -1602,7 +1592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1653,7 +1643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1682,7 +1672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1711,7 +1701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1740,7 +1730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -1769,7 +1759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>190</v>
       </c>
@@ -1795,7 +1785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1824,7 +1814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>190</v>
       </c>
@@ -1850,7 +1840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>190</v>
       </c>
@@ -1876,7 +1866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>190</v>
       </c>
@@ -1945,7 +1935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -1974,7 +1964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -2003,7 +1993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -2061,7 +2051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -2084,10 +2074,10 @@
         <v>291</v>
       </c>
       <c r="I26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -2113,7 +2103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>191</v>
       </c>
@@ -2142,7 +2132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>190</v>
       </c>
@@ -2171,7 +2161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>190</v>
       </c>
@@ -2309,7 +2299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2338,7 +2328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -2367,7 +2357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -2396,7 +2386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -2425,7 +2415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>190</v>
       </c>
@@ -2451,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>190</v>
       </c>
@@ -2564,7 +2554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -2619,7 +2609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>191</v>
       </c>
@@ -2645,7 +2635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>191</v>
       </c>
@@ -2674,7 +2664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>191</v>
       </c>
@@ -2703,7 +2693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>44</v>
       </c>
@@ -2732,7 +2722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -2819,7 +2809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>44</v>
       </c>
@@ -2848,7 +2838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>44</v>
       </c>
@@ -2961,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>16</v>
       </c>
@@ -2990,7 +2980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>191</v>
       </c>
@@ -3071,7 +3061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>44</v>
       </c>
@@ -3129,7 +3119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>44</v>
       </c>
@@ -3178,7 +3168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>191</v>
       </c>
@@ -3204,7 +3194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>191</v>
       </c>
@@ -3230,7 +3220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>191</v>
       </c>
@@ -3256,7 +3246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>191</v>
       </c>
@@ -3285,7 +3275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>191</v>
       </c>
@@ -3343,7 +3333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>190</v>
       </c>
@@ -3577,7 +3567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>44</v>
       </c>
@@ -3597,7 +3587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -3626,7 +3616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -3794,7 +3784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -3820,7 +3810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -3953,7 +3943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -3976,10 +3966,10 @@
         <v>291</v>
       </c>
       <c r="I97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>44</v>
       </c>
@@ -4372,7 +4362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>44</v>
       </c>
@@ -4401,7 +4391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -4470,7 +4460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>44</v>
       </c>
@@ -4499,7 +4489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>44</v>
       </c>
@@ -4609,7 +4599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>44</v>
       </c>
@@ -4638,7 +4628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>190</v>
       </c>
@@ -4664,7 +4654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>190</v>
       </c>
@@ -4693,7 +4683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>190</v>
       </c>
@@ -4722,7 +4712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>44</v>
       </c>
@@ -4927,7 +4917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>16</v>
       </c>
@@ -4956,7 +4946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>44</v>
       </c>
@@ -4985,7 +4975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -5008,10 +4998,10 @@
         <v>291</v>
       </c>
       <c r="I136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -5040,7 +5030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -5069,7 +5059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>16</v>
       </c>
@@ -5098,7 +5088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>44</v>
       </c>
@@ -5156,7 +5146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>25</v>
       </c>
@@ -5185,7 +5175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>25</v>
       </c>
@@ -5214,7 +5204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -5295,7 +5285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>190</v>
       </c>
@@ -5332,7 +5322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -5355,10 +5345,10 @@
         <v>291</v>
       </c>
       <c r="I149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -5381,10 +5371,10 @@
         <v>291</v>
       </c>
       <c r="I150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>44</v>
       </c>
@@ -5488,7 +5478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>190</v>
       </c>
@@ -5514,7 +5504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>44</v>
       </c>
@@ -5543,7 +5533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>16</v>
       </c>
@@ -5572,7 +5562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>44</v>
       </c>
@@ -5592,7 +5582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>44</v>
       </c>
@@ -5701,7 +5691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>44</v>
       </c>
@@ -5756,7 +5746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>44</v>
       </c>
@@ -5785,7 +5775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>44</v>
       </c>
@@ -5892,7 +5882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>44</v>
       </c>
@@ -5950,7 +5940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>44</v>
       </c>
@@ -6083,7 +6073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>44</v>
       </c>
@@ -6138,7 +6128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>16</v>
       </c>
@@ -6167,7 +6157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>16</v>
       </c>
@@ -6225,7 +6215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>190</v>
       </c>
@@ -6277,7 +6267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>44</v>
       </c>
@@ -6306,7 +6296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>190</v>
       </c>
@@ -6332,7 +6322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>44</v>
       </c>
@@ -6390,7 +6380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>190</v>
       </c>
@@ -6497,7 +6487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>190</v>
       </c>
@@ -6592,7 +6582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>44</v>
       </c>
@@ -6702,7 +6692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -6725,7 +6715,7 @@
         <v>289</v>
       </c>
       <c r="I201">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
@@ -6757,7 +6747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>44</v>
       </c>
@@ -6786,7 +6776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>44</v>
       </c>
@@ -6815,7 +6805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>25</v>
       </c>
@@ -6844,7 +6834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>25</v>
       </c>
@@ -6873,7 +6863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>25</v>
       </c>
@@ -6931,7 +6921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>190</v>
       </c>
@@ -6968,7 +6958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>190</v>
       </c>
@@ -7020,7 +7010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>44</v>
       </c>
@@ -7078,7 +7068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>190</v>
       </c>
@@ -7107,7 +7097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>190</v>
       </c>
@@ -7133,7 +7123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>190</v>
       </c>
@@ -7290,7 +7280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>25</v>
       </c>
@@ -7319,7 +7309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>25</v>
       </c>
@@ -7348,7 +7338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>25</v>
       </c>
@@ -7377,7 +7367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>44</v>
       </c>
@@ -7432,7 +7422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>190</v>
       </c>
@@ -7487,7 +7477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>190</v>
       </c>
@@ -7513,7 +7503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>44</v>
       </c>
@@ -7597,7 +7587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -7620,10 +7610,10 @@
         <v>291</v>
       </c>
       <c r="I234">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -7646,7 +7636,7 @@
         <v>291</v>
       </c>
       <c r="I235">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
@@ -7678,7 +7668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>190</v>
       </c>
@@ -7837,7 +7827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>190</v>
       </c>
@@ -7863,7 +7853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>190</v>
       </c>
@@ -7978,7 +7968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>44</v>
       </c>
@@ -8007,7 +7997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>190</v>
       </c>
@@ -8033,7 +8023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>190</v>
       </c>
@@ -8108,7 +8098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>44</v>
       </c>
@@ -8200,7 +8190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>18</v>
       </c>
@@ -8220,10 +8210,10 @@
         <v>291</v>
       </c>
       <c r="I258">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>18</v>
       </c>
@@ -8246,7 +8236,7 @@
         <v>291</v>
       </c>
       <c r="I259">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
@@ -8358,7 +8348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>25</v>
       </c>
@@ -8384,7 +8374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>44</v>
       </c>
@@ -8413,7 +8403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>44</v>
       </c>
@@ -8442,7 +8432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>190</v>
       </c>
@@ -8468,7 +8458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>190</v>
       </c>
@@ -8523,7 +8513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>44</v>
       </c>
@@ -8569,7 +8559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>25</v>
       </c>
@@ -8598,7 +8588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>25</v>
       </c>
@@ -8627,7 +8617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>25</v>
       </c>
@@ -8844,7 +8834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>190</v>
       </c>
@@ -8870,7 +8860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>190</v>
       </c>
@@ -8896,7 +8886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>190</v>
       </c>
@@ -9003,7 +8993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>44</v>
       </c>
@@ -9150,7 +9140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>44</v>
       </c>
@@ -9179,7 +9169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>44</v>
       </c>
@@ -9266,7 +9256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>191</v>
       </c>
@@ -9318,7 +9308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>25</v>
       </c>
@@ -9347,7 +9337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>25</v>
       </c>
@@ -9376,7 +9366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>25</v>
       </c>
@@ -9405,7 +9395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>25</v>
       </c>
@@ -9564,7 +9554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>44</v>
       </c>
@@ -9706,7 +9696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>18</v>
       </c>
@@ -9732,7 +9722,7 @@
         <v>289</v>
       </c>
       <c r="I315">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
@@ -9764,7 +9754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>44</v>
       </c>
@@ -9793,7 +9783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>44</v>
       </c>
@@ -9848,7 +9838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>44</v>
       </c>
@@ -9877,7 +9867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>190</v>
       </c>
@@ -10030,7 +10020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>44</v>
       </c>
@@ -10059,7 +10049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>190</v>
       </c>
@@ -10085,7 +10075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>190</v>
       </c>
@@ -10111,7 +10101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>190</v>
       </c>
@@ -10137,7 +10127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>190</v>
       </c>
@@ -10192,7 +10182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>190</v>
       </c>
@@ -10218,7 +10208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>44</v>
       </c>
@@ -10247,7 +10237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>44</v>
       </c>
@@ -10357,7 +10347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>190</v>
       </c>
@@ -10493,7 +10483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>190</v>
       </c>
@@ -10533,7 +10523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>25</v>
       </c>
@@ -10544,7 +10534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>190</v>
       </c>
@@ -10570,7 +10560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>190</v>
       </c>
@@ -10622,7 +10612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>190</v>
       </c>
@@ -10648,7 +10638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>190</v>
       </c>
@@ -10707,7 +10697,17 @@
   <autoFilter ref="A1:I352">
     <filterColumn colId="0">
       <filters>
+        <filter val="AmfiReptie"/>
+        <filter val="Libellen"/>
+        <filter val="Planten"/>
+        <filter val="Vlinders"/>
+        <filter val="Vogels"/>
         <filter val="Zoogdieren"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="8">
+      <filters>
+        <filter val="1"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:I352">

--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1676" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="342">
   <si>
     <t>Soort</t>
   </si>
@@ -1095,18 +1095,7 @@
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1453,7 +1442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1508,7 +1497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1643,7 +1632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1672,7 +1661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1701,7 +1690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1759,7 +1748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>190</v>
       </c>
@@ -1814,7 +1803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>190</v>
       </c>
@@ -1840,7 +1829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>190</v>
       </c>
@@ -1866,7 +1855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>190</v>
       </c>
@@ -1877,7 +1866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1894,7 +1883,7 @@
         <v>20</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G20" t="s">
         <v>309</v>
@@ -1964,7 +1953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1993,7 +1982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -2022,7 +2011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -2039,7 +2028,7 @@
         <v>20</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G25" t="s">
         <v>309</v>
@@ -2051,7 +2040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -2077,7 +2066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -2132,7 +2121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>190</v>
       </c>
@@ -2161,7 +2150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>190</v>
       </c>
@@ -2328,7 +2317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -2357,7 +2346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -2386,7 +2375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -2415,7 +2404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>190</v>
       </c>
@@ -2441,7 +2430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>190</v>
       </c>
@@ -2710,7 +2699,7 @@
         <v>20</v>
       </c>
       <c r="F50">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G50" t="s">
         <v>309</v>
@@ -2751,7 +2740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>44</v>
       </c>
@@ -2768,7 +2757,7 @@
         <v>20</v>
       </c>
       <c r="F52">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G52" t="s">
         <v>309</v>
@@ -2780,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>44</v>
       </c>
@@ -2797,7 +2786,7 @@
         <v>20</v>
       </c>
       <c r="F53">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G53" t="s">
         <v>309</v>
@@ -2867,7 +2856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>44</v>
       </c>
@@ -2884,7 +2873,7 @@
         <v>20</v>
       </c>
       <c r="F56">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G56" t="s">
         <v>309</v>
@@ -2922,7 +2911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>44</v>
       </c>
@@ -2939,7 +2928,7 @@
         <v>20</v>
       </c>
       <c r="F58">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G58" t="s">
         <v>309</v>
@@ -2951,7 +2940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>16</v>
       </c>
@@ -3090,7 +3079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>44</v>
       </c>
@@ -3107,7 +3096,7 @@
         <v>20</v>
       </c>
       <c r="F64">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G64" t="s">
         <v>309</v>
@@ -3126,6 +3115,9 @@
       <c r="B65" t="s">
         <v>317</v>
       </c>
+      <c r="C65" t="s">
+        <v>263</v>
+      </c>
       <c r="D65">
         <v>0.16</v>
       </c>
@@ -3133,13 +3125,19 @@
         <v>20</v>
       </c>
       <c r="F65">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="G65" t="s">
+        <v>309</v>
+      </c>
+      <c r="H65" t="s">
+        <v>290</v>
       </c>
       <c r="I65">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>191</v>
       </c>
@@ -3304,7 +3302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>44</v>
       </c>
@@ -3321,7 +3319,7 @@
         <v>20</v>
       </c>
       <c r="F72">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G72" t="s">
         <v>309</v>
@@ -3333,7 +3331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>190</v>
       </c>
@@ -3574,6 +3572,9 @@
       <c r="B82" t="s">
         <v>319</v>
       </c>
+      <c r="C82" t="s">
+        <v>263</v>
+      </c>
       <c r="D82">
         <v>0.16</v>
       </c>
@@ -3581,13 +3582,19 @@
         <v>20</v>
       </c>
       <c r="F82">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="G82" t="s">
+        <v>309</v>
+      </c>
+      <c r="H82" t="s">
+        <v>290</v>
       </c>
       <c r="I82">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -3616,7 +3623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -3700,7 +3707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>44</v>
       </c>
@@ -3717,7 +3724,7 @@
         <v>20</v>
       </c>
       <c r="F87">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G87" t="s">
         <v>309</v>
@@ -3784,7 +3791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -3810,7 +3817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -3914,7 +3921,7 @@
       </c>
       <c r="L95" s="1"/>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>44</v>
       </c>
@@ -3931,7 +3938,7 @@
         <v>20</v>
       </c>
       <c r="F96">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G96" t="s">
         <v>309</v>
@@ -3943,7 +3950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -4391,7 +4398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -4628,7 +4635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>190</v>
       </c>
@@ -4654,7 +4661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>190</v>
       </c>
@@ -4683,7 +4690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>190</v>
       </c>
@@ -4719,6 +4726,9 @@
       <c r="B126" t="s">
         <v>324</v>
       </c>
+      <c r="C126" t="s">
+        <v>263</v>
+      </c>
       <c r="D126">
         <v>0.16</v>
       </c>
@@ -4726,7 +4736,13 @@
         <v>20</v>
       </c>
       <c r="F126">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="G126" t="s">
+        <v>309</v>
+      </c>
+      <c r="H126" t="s">
+        <v>290</v>
       </c>
       <c r="I126">
         <v>1</v>
@@ -4758,7 +4774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>44</v>
       </c>
@@ -4775,7 +4791,7 @@
         <v>20</v>
       </c>
       <c r="F128">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G128" t="s">
         <v>309</v>
@@ -4839,7 +4855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>191</v>
       </c>
@@ -4865,7 +4881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>191</v>
       </c>
@@ -4917,7 +4933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>16</v>
       </c>
@@ -4975,7 +4991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -5001,7 +5017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -5030,7 +5046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -5059,7 +5075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>16</v>
       </c>
@@ -5117,7 +5133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>44</v>
       </c>
@@ -5134,7 +5150,7 @@
         <v>20</v>
       </c>
       <c r="F141">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G141" t="s">
         <v>309</v>
@@ -5146,7 +5162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>25</v>
       </c>
@@ -5175,7 +5191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>25</v>
       </c>
@@ -5204,7 +5220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -5285,7 +5301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>190</v>
       </c>
@@ -5322,7 +5338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -5348,7 +5364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -5381,6 +5397,9 @@
       <c r="B151" t="s">
         <v>326</v>
       </c>
+      <c r="C151" t="s">
+        <v>263</v>
+      </c>
       <c r="D151">
         <v>0.16</v>
       </c>
@@ -5388,7 +5407,13 @@
         <v>20</v>
       </c>
       <c r="F151">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="G151" t="s">
+        <v>309</v>
+      </c>
+      <c r="H151" t="s">
+        <v>290</v>
       </c>
       <c r="I151">
         <v>1</v>
@@ -5478,7 +5503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>190</v>
       </c>
@@ -5533,7 +5558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>16</v>
       </c>
@@ -5569,6 +5594,9 @@
       <c r="B158" t="s">
         <v>327</v>
       </c>
+      <c r="C158" t="s">
+        <v>263</v>
+      </c>
       <c r="D158">
         <v>0.16</v>
       </c>
@@ -5576,7 +5604,13 @@
         <v>20</v>
       </c>
       <c r="F158">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="G158" t="s">
+        <v>309</v>
+      </c>
+      <c r="H158" t="s">
+        <v>290</v>
       </c>
       <c r="I158">
         <v>1</v>
@@ -5792,7 +5826,7 @@
         <v>20</v>
       </c>
       <c r="F167">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G167" t="s">
         <v>309</v>
@@ -5911,7 +5945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>44</v>
       </c>
@@ -5928,7 +5962,7 @@
         <v>20</v>
       </c>
       <c r="F172">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G172" t="s">
         <v>309</v>
@@ -6128,7 +6162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>16</v>
       </c>
@@ -6157,7 +6191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>16</v>
       </c>
@@ -6186,7 +6220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>44</v>
       </c>
@@ -6203,7 +6237,7 @@
         <v>20</v>
       </c>
       <c r="F182">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G182" t="s">
         <v>309</v>
@@ -6215,7 +6249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>190</v>
       </c>
@@ -6296,7 +6330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>190</v>
       </c>
@@ -6351,7 +6385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>44</v>
       </c>
@@ -6368,7 +6402,7 @@
         <v>20</v>
       </c>
       <c r="F188">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G188" t="s">
         <v>273</v>
@@ -6380,7 +6414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>190</v>
       </c>
@@ -6487,7 +6521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>190</v>
       </c>
@@ -6513,7 +6547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>44</v>
       </c>
@@ -6530,7 +6564,7 @@
         <v>20</v>
       </c>
       <c r="F194">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G194" t="s">
         <v>309</v>
@@ -6553,7 +6587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>44</v>
       </c>
@@ -6570,7 +6604,7 @@
         <v>20</v>
       </c>
       <c r="F196">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G196" t="s">
         <v>309</v>
@@ -6692,7 +6726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -6718,7 +6752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>44</v>
       </c>
@@ -6735,7 +6769,7 @@
         <v>20</v>
       </c>
       <c r="F202">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G202" t="s">
         <v>309</v>
@@ -6805,7 +6839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>25</v>
       </c>
@@ -6834,7 +6868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>25</v>
       </c>
@@ -6863,7 +6897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>25</v>
       </c>
@@ -6892,7 +6926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>44</v>
       </c>
@@ -6909,7 +6943,7 @@
         <v>20</v>
       </c>
       <c r="F208">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G208" t="s">
         <v>309</v>
@@ -6921,7 +6955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>190</v>
       </c>
@@ -6958,7 +6992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>190</v>
       </c>
@@ -7068,7 +7102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>190</v>
       </c>
@@ -7097,7 +7131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>190</v>
       </c>
@@ -7123,7 +7157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>190</v>
       </c>
@@ -7280,7 +7314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>25</v>
       </c>
@@ -7309,7 +7343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>25</v>
       </c>
@@ -7338,7 +7372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>25</v>
       </c>
@@ -7422,7 +7456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>190</v>
       </c>
@@ -7448,7 +7482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>44</v>
       </c>
@@ -7465,7 +7499,7 @@
         <v>20</v>
       </c>
       <c r="F229">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G229" t="s">
         <v>309</v>
@@ -7477,7 +7511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>190</v>
       </c>
@@ -7532,7 +7566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>44</v>
       </c>
@@ -7549,7 +7583,7 @@
         <v>20</v>
       </c>
       <c r="F232">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G232" t="s">
         <v>309</v>
@@ -7587,7 +7621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -7613,7 +7647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -7639,7 +7673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>44</v>
       </c>
@@ -7656,7 +7690,7 @@
         <v>20</v>
       </c>
       <c r="F236">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G236" t="s">
         <v>309</v>
@@ -7668,7 +7702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>190</v>
       </c>
@@ -7694,7 +7728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>44</v>
       </c>
@@ -7711,7 +7745,7 @@
         <v>20</v>
       </c>
       <c r="F238">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G238" t="s">
         <v>309</v>
@@ -7827,7 +7861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>190</v>
       </c>
@@ -7853,7 +7887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>190</v>
       </c>
@@ -7997,7 +8031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>190</v>
       </c>
@@ -8023,7 +8057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>190</v>
       </c>
@@ -8069,7 +8103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>44</v>
       </c>
@@ -8190,7 +8224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>18</v>
       </c>
@@ -8213,7 +8247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>18</v>
       </c>
@@ -8279,7 +8313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>44</v>
       </c>
@@ -8296,7 +8330,7 @@
         <v>20</v>
       </c>
       <c r="F262">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G262" t="s">
         <v>309</v>
@@ -8308,7 +8342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>44</v>
       </c>
@@ -8348,7 +8382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>25</v>
       </c>
@@ -8432,7 +8466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>190</v>
       </c>
@@ -8458,7 +8492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>190</v>
       </c>
@@ -8520,6 +8554,9 @@
       <c r="B271" t="s">
         <v>336</v>
       </c>
+      <c r="C271" t="s">
+        <v>263</v>
+      </c>
       <c r="D271">
         <v>0.16</v>
       </c>
@@ -8527,7 +8564,13 @@
         <v>20</v>
       </c>
       <c r="F271">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="G271" t="s">
+        <v>309</v>
+      </c>
+      <c r="H271" t="s">
+        <v>290</v>
       </c>
       <c r="I271">
         <v>1</v>
@@ -8559,7 +8602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>25</v>
       </c>
@@ -8588,7 +8631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>25</v>
       </c>
@@ -8617,7 +8660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>25</v>
       </c>
@@ -8701,7 +8744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>44</v>
       </c>
@@ -8718,7 +8761,7 @@
         <v>20</v>
       </c>
       <c r="F278">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G278" t="s">
         <v>309</v>
@@ -8834,7 +8877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>190</v>
       </c>
@@ -8860,7 +8903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>190</v>
       </c>
@@ -8886,7 +8929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>190</v>
       </c>
@@ -9085,7 +9128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>44</v>
       </c>
@@ -9308,7 +9351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>25</v>
       </c>
@@ -9337,7 +9380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>25</v>
       </c>
@@ -9366,7 +9409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>25</v>
       </c>
@@ -9395,7 +9438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>25</v>
       </c>
@@ -9696,7 +9739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>18</v>
       </c>
@@ -9725,7 +9768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>44</v>
       </c>
@@ -9742,7 +9785,7 @@
         <v>20</v>
       </c>
       <c r="F316">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G316" t="s">
         <v>309</v>
@@ -9867,7 +9910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>190</v>
       </c>
@@ -9893,7 +9936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>191</v>
       </c>
@@ -9933,7 +9976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>44</v>
       </c>
@@ -9950,7 +9993,7 @@
         <v>20</v>
       </c>
       <c r="F324">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G324" t="s">
         <v>309</v>
@@ -9962,7 +10005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>44</v>
       </c>
@@ -9979,7 +10022,7 @@
         <v>20</v>
       </c>
       <c r="F325">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G325" t="s">
         <v>309</v>
@@ -10049,7 +10092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>190</v>
       </c>
@@ -10075,7 +10118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>190</v>
       </c>
@@ -10101,7 +10144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>190</v>
       </c>
@@ -10127,7 +10170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>190</v>
       </c>
@@ -10153,7 +10196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>44</v>
       </c>
@@ -10182,7 +10225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>190</v>
       </c>
@@ -10266,7 +10309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>44</v>
       </c>
@@ -10283,7 +10326,7 @@
         <v>20</v>
       </c>
       <c r="F336">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G336" t="s">
         <v>309</v>
@@ -10347,7 +10390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>190</v>
       </c>
@@ -10402,7 +10445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>44</v>
       </c>
@@ -10419,7 +10462,7 @@
         <v>20</v>
       </c>
       <c r="F341">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G341" t="s">
         <v>309</v>
@@ -10483,7 +10526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>190</v>
       </c>
@@ -10523,7 +10566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>25</v>
       </c>
@@ -10534,7 +10577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>190</v>
       </c>
@@ -10560,7 +10603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>190</v>
       </c>
@@ -10612,7 +10655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>190</v>
       </c>
@@ -10638,7 +10681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>190</v>
       </c>
@@ -10697,17 +10740,7 @@
   <autoFilter ref="A1:I352">
     <filterColumn colId="0">
       <filters>
-        <filter val="AmfiReptie"/>
-        <filter val="Libellen"/>
         <filter val="Planten"/>
-        <filter val="Vlinders"/>
-        <filter val="Vogels"/>
-        <filter val="Zoogdieren"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="8">
-      <filters>
-        <filter val="1"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:I352">

--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -4947,6 +4947,9 @@
       <c r="E133">
         <v>50</v>
       </c>
+      <c r="F133">
+        <v>2000</v>
+      </c>
       <c r="G133" t="s">
         <v>308</v>
       </c>
@@ -6107,6 +6110,9 @@
       <c r="E176">
         <v>10</v>
       </c>
+      <c r="F176">
+        <v>1000</v>
+      </c>
       <c r="G176" t="s">
         <v>272</v>
       </c>
@@ -6133,6 +6139,9 @@
       <c r="E177">
         <v>50</v>
       </c>
+      <c r="F177">
+        <v>1000</v>
+      </c>
       <c r="G177" t="s">
         <v>272</v>
       </c>
@@ -8643,6 +8652,9 @@
       <c r="E272">
         <v>50</v>
       </c>
+      <c r="F272">
+        <v>1000</v>
+      </c>
       <c r="G272" t="s">
         <v>272</v>
       </c>
@@ -9638,6 +9650,9 @@
       <c r="E309">
         <v>50</v>
       </c>
+      <c r="F309">
+        <v>1000</v>
+      </c>
       <c r="G309" t="s">
         <v>272</v>
       </c>
@@ -9663,6 +9678,9 @@
       </c>
       <c r="E310">
         <v>50</v>
+      </c>
+      <c r="F310">
+        <v>1000</v>
       </c>
       <c r="G310" t="s">
         <v>272</v>

--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11496" windowHeight="7800"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="11496" windowHeight="7800"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -1394,6 +1394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O358"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1461,7 +1462,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1502,7 +1503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1546,7 +1547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1587,7 +1588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1631,7 +1632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -1675,7 +1676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1719,7 +1720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1763,7 +1764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>332</v>
       </c>
@@ -1789,7 +1790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -1815,7 +1816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1859,7 +1860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1903,7 +1904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1947,7 +1948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -1991,7 +1992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>189</v>
       </c>
@@ -2038,7 +2039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -2082,7 +2083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>189</v>
       </c>
@@ -2129,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>189</v>
       </c>
@@ -2176,7 +2177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>189</v>
       </c>
@@ -2211,7 +2212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>189</v>
       </c>
@@ -2246,7 +2247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -2290,7 +2291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>221</v>
       </c>
@@ -2334,7 +2335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -2378,7 +2379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -2422,7 +2423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -2466,7 +2467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>44</v>
       </c>
@@ -2510,7 +2511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -2554,7 +2555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>189</v>
       </c>
@@ -2601,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>190</v>
       </c>
@@ -2645,7 +2646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>189</v>
       </c>
@@ -2692,7 +2693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>189</v>
       </c>
@@ -2739,7 +2740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -2783,7 +2784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -2827,7 +2828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -2871,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>332</v>
       </c>
@@ -2897,7 +2898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>332</v>
       </c>
@@ -2923,7 +2924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -2967,7 +2968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -3011,7 +3012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -3055,7 +3056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>16</v>
       </c>
@@ -3099,7 +3100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>189</v>
       </c>
@@ -3146,7 +3147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>189</v>
       </c>
@@ -3193,7 +3194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -3237,7 +3238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -3281,7 +3282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>25</v>
       </c>
@@ -3325,7 +3326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -3369,7 +3370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>16</v>
       </c>
@@ -3410,7 +3411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>190</v>
       </c>
@@ -3451,7 +3452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>190</v>
       </c>
@@ -3495,7 +3496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>190</v>
       </c>
@@ -3539,7 +3540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -3583,7 +3584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>44</v>
       </c>
@@ -3627,7 +3628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>44</v>
       </c>
@@ -3671,7 +3672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>44</v>
       </c>
@@ -3715,7 +3716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>44</v>
       </c>
@@ -3759,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>44</v>
       </c>
@@ -3803,7 +3804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>44</v>
       </c>
@@ -3847,7 +3848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>189</v>
       </c>
@@ -3894,7 +3895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>44</v>
       </c>
@@ -3938,7 +3939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>16</v>
       </c>
@@ -3982,7 +3983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>190</v>
       </c>
@@ -4026,7 +4027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>189</v>
       </c>
@@ -4073,7 +4074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>189</v>
       </c>
@@ -4120,7 +4121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>44</v>
       </c>
@@ -4164,7 +4165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>44</v>
       </c>
@@ -4208,7 +4209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>44</v>
       </c>
@@ -4252,7 +4253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>190</v>
       </c>
@@ -4269,7 +4270,7 @@
         <v>20</v>
       </c>
       <c r="F67">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="G67" t="s">
         <v>308</v>
@@ -4296,7 +4297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>190</v>
       </c>
@@ -4337,7 +4338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>190</v>
       </c>
@@ -4378,7 +4379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>190</v>
       </c>
@@ -4419,7 +4420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>190</v>
       </c>
@@ -4463,7 +4464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>190</v>
       </c>
@@ -4507,7 +4508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -4551,7 +4552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>189</v>
       </c>
@@ -4598,7 +4599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>332</v>
       </c>
@@ -4624,7 +4625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -4665,7 +4666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>25</v>
       </c>
@@ -4709,7 +4710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>25</v>
       </c>
@@ -4753,7 +4754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>189</v>
       </c>
@@ -4800,7 +4801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>189</v>
       </c>
@@ -4847,7 +4848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>32</v>
       </c>
@@ -4891,7 +4892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>189</v>
       </c>
@@ -4938,7 +4939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>44</v>
       </c>
@@ -4982,7 +4983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -5026,7 +5027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>16</v>
       </c>
@@ -5070,7 +5071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>189</v>
       </c>
@@ -5117,7 +5118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>40</v>
       </c>
@@ -5161,7 +5162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>44</v>
       </c>
@@ -5205,7 +5206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -5249,7 +5250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -5293,7 +5294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -5334,7 +5335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>25</v>
       </c>
@@ -5375,7 +5376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>332</v>
       </c>
@@ -5401,7 +5402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>332</v>
       </c>
@@ -5427,7 +5428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -5471,7 +5472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>25</v>
       </c>
@@ -5515,7 +5516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>44</v>
       </c>
@@ -5559,7 +5560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -5603,7 +5604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>44</v>
       </c>
@@ -5647,7 +5648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>25</v>
       </c>
@@ -5691,7 +5692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>25</v>
       </c>
@@ -5735,7 +5736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>21</v>
       </c>
@@ -5779,7 +5780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>21</v>
       </c>
@@ -5823,7 +5824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>189</v>
       </c>
@@ -5870,7 +5871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>189</v>
       </c>
@@ -5917,7 +5918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>189</v>
       </c>
@@ -5964,7 +5965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>189</v>
       </c>
@@ -6011,7 +6012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>189</v>
       </c>
@@ -6058,7 +6059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>189</v>
       </c>
@@ -6105,7 +6106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>189</v>
       </c>
@@ -6152,7 +6153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>189</v>
       </c>
@@ -6199,7 +6200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>189</v>
       </c>
@@ -6246,7 +6247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>332</v>
       </c>
@@ -6272,7 +6273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>44</v>
       </c>
@@ -6316,7 +6317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>16</v>
       </c>
@@ -6360,7 +6361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>332</v>
       </c>
@@ -6386,7 +6387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>41</v>
       </c>
@@ -6430,7 +6431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>44</v>
       </c>
@@ -6474,7 +6475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>44</v>
       </c>
@@ -6518,7 +6519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>189</v>
       </c>
@@ -6565,7 +6566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>189</v>
       </c>
@@ -6612,7 +6613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>16</v>
       </c>
@@ -6656,7 +6657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>44</v>
       </c>
@@ -6700,7 +6701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>189</v>
       </c>
@@ -6747,7 +6748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>189</v>
       </c>
@@ -6794,7 +6795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>189</v>
       </c>
@@ -6841,7 +6842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>44</v>
       </c>
@@ -6885,7 +6886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>42</v>
       </c>
@@ -6926,7 +6927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>44</v>
       </c>
@@ -6970,7 +6971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>189</v>
       </c>
@@ -7017,7 +7018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>189</v>
       </c>
@@ -7064,7 +7065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>190</v>
       </c>
@@ -7108,7 +7109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>190</v>
       </c>
@@ -7152,7 +7153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -7196,7 +7197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>16</v>
       </c>
@@ -7240,7 +7241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>44</v>
       </c>
@@ -7284,7 +7285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -7328,7 +7329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -7372,7 +7373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>16</v>
       </c>
@@ -7416,7 +7417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>16</v>
       </c>
@@ -7460,7 +7461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>44</v>
       </c>
@@ -7504,7 +7505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>44</v>
       </c>
@@ -7548,7 +7549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>25</v>
       </c>
@@ -7592,7 +7593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -7636,7 +7637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>25</v>
       </c>
@@ -7680,7 +7681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>189</v>
       </c>
@@ -7727,7 +7728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>16</v>
       </c>
@@ -7768,7 +7769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>189</v>
       </c>
@@ -7815,7 +7816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>332</v>
       </c>
@@ -7841,7 +7842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -7885,7 +7886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -7929,7 +7930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>44</v>
       </c>
@@ -7973,7 +7974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>16</v>
       </c>
@@ -8017,7 +8018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>25</v>
       </c>
@@ -8061,7 +8062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>25</v>
       </c>
@@ -8105,7 +8106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>189</v>
       </c>
@@ -8152,7 +8153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>44</v>
       </c>
@@ -8196,7 +8197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>16</v>
       </c>
@@ -8240,7 +8241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>44</v>
       </c>
@@ -8284,7 +8285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>44</v>
       </c>
@@ -8328,7 +8329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>332</v>
       </c>
@@ -8354,7 +8355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>41</v>
       </c>
@@ -8380,7 +8381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>16</v>
       </c>
@@ -8424,7 +8425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>16</v>
       </c>
@@ -8468,7 +8469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>44</v>
       </c>
@@ -8512,7 +8513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>189</v>
       </c>
@@ -8559,7 +8560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>44</v>
       </c>
@@ -8603,7 +8604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>44</v>
       </c>
@@ -8647,7 +8648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>189</v>
       </c>
@@ -8694,7 +8695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>189</v>
       </c>
@@ -8741,7 +8742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>189</v>
       </c>
@@ -8788,7 +8789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>44</v>
       </c>
@@ -8832,7 +8833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>44</v>
       </c>
@@ -8876,7 +8877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>44</v>
       </c>
@@ -8920,7 +8921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>189</v>
       </c>
@@ -8967,7 +8968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>189</v>
       </c>
@@ -9014,7 +9015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -9058,7 +9059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -9102,7 +9103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>44</v>
       </c>
@@ -9146,7 +9147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>189</v>
       </c>
@@ -9193,7 +9194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>16</v>
       </c>
@@ -9237,7 +9238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>16</v>
       </c>
@@ -9281,7 +9282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>44</v>
       </c>
@@ -9325,7 +9326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>189</v>
       </c>
@@ -9372,7 +9373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>189</v>
       </c>
@@ -9419,7 +9420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>44</v>
       </c>
@@ -9463,7 +9464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>189</v>
       </c>
@@ -9510,7 +9511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>44</v>
       </c>
@@ -9554,7 +9555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>44</v>
       </c>
@@ -9598,7 +9599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>189</v>
       </c>
@@ -9645,7 +9646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>189</v>
       </c>
@@ -9692,7 +9693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>189</v>
       </c>
@@ -9739,7 +9740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>189</v>
       </c>
@@ -9833,7 +9834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>44</v>
       </c>
@@ -9877,7 +9878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>332</v>
       </c>
@@ -9903,7 +9904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>44</v>
       </c>
@@ -9947,7 +9948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>44</v>
       </c>
@@ -9991,7 +9992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>40</v>
       </c>
@@ -10035,7 +10036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>189</v>
       </c>
@@ -10082,7 +10083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>189</v>
       </c>
@@ -10129,7 +10130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -10173,7 +10174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>44</v>
       </c>
@@ -10217,7 +10218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>44</v>
       </c>
@@ -10261,7 +10262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>44</v>
       </c>
@@ -10305,7 +10306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>25</v>
       </c>
@@ -10349,7 +10350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>25</v>
       </c>
@@ -10393,7 +10394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>25</v>
       </c>
@@ -10437,7 +10438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>44</v>
       </c>
@@ -10481,7 +10482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>189</v>
       </c>
@@ -10528,7 +10529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>332</v>
       </c>
@@ -10554,7 +10555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>189</v>
       </c>
@@ -10601,7 +10602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>16</v>
       </c>
@@ -10642,7 +10643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>44</v>
       </c>
@@ -10686,7 +10687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>221</v>
       </c>
@@ -10730,7 +10731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>189</v>
       </c>
@@ -10777,7 +10778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>189</v>
       </c>
@@ -10824,7 +10825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>189</v>
       </c>
@@ -10871,7 +10872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>43</v>
       </c>
@@ -10912,7 +10913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>43</v>
       </c>
@@ -10953,7 +10954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>25</v>
       </c>
@@ -10994,7 +10995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>25</v>
       </c>
@@ -11035,7 +11036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>25</v>
       </c>
@@ -11076,7 +11077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>25</v>
       </c>
@@ -11120,7 +11121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>25</v>
       </c>
@@ -11164,7 +11165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>25</v>
       </c>
@@ -11208,7 +11209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>44</v>
       </c>
@@ -11252,7 +11253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>189</v>
       </c>
@@ -11299,7 +11300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>189</v>
       </c>
@@ -11346,7 +11347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>44</v>
       </c>
@@ -11390,7 +11391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>189</v>
       </c>
@@ -11437,7 +11438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>44</v>
       </c>
@@ -11481,7 +11482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>44</v>
       </c>
@@ -11525,7 +11526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>43</v>
       </c>
@@ -11566,7 +11567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -11610,7 +11611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -11654,7 +11655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>44</v>
       </c>
@@ -11698,7 +11699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>189</v>
       </c>
@@ -11745,7 +11746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>44</v>
       </c>
@@ -11789,7 +11790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>189</v>
       </c>
@@ -11836,7 +11837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>189</v>
       </c>
@@ -11883,7 +11884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>16</v>
       </c>
@@ -11924,7 +11925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>189</v>
       </c>
@@ -11971,7 +11972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>189</v>
       </c>
@@ -12018,7 +12019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>189</v>
       </c>
@@ -12065,7 +12066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>189</v>
       </c>
@@ -12112,7 +12113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>41</v>
       </c>
@@ -12138,7 +12139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>25</v>
       </c>
@@ -12179,7 +12180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>25</v>
       </c>
@@ -12220,7 +12221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>44</v>
       </c>
@@ -12264,7 +12265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>189</v>
       </c>
@@ -12311,7 +12312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>189</v>
       </c>
@@ -12358,7 +12359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>21</v>
       </c>
@@ -12393,7 +12394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>44</v>
       </c>
@@ -12437,7 +12438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>44</v>
       </c>
@@ -12481,7 +12482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>189</v>
       </c>
@@ -12528,7 +12529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>189</v>
       </c>
@@ -12575,7 +12576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>332</v>
       </c>
@@ -12601,7 +12602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>18</v>
       </c>
@@ -12642,7 +12643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>18</v>
       </c>
@@ -12686,7 +12687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>332</v>
       </c>
@@ -12712,7 +12713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>221</v>
       </c>
@@ -12756,7 +12757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>44</v>
       </c>
@@ -12800,7 +12801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>44</v>
       </c>
@@ -12844,7 +12845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>41</v>
       </c>
@@ -12870,7 +12871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>25</v>
       </c>
@@ -12914,7 +12915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>44</v>
       </c>
@@ -12958,7 +12959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>44</v>
       </c>
@@ -13002,7 +13003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>189</v>
       </c>
@@ -13049,7 +13050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>189</v>
       </c>
@@ -13096,7 +13097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>221</v>
       </c>
@@ -13140,7 +13141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>44</v>
       </c>
@@ -13184,7 +13185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>16</v>
       </c>
@@ -13228,7 +13229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>25</v>
       </c>
@@ -13272,7 +13273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>25</v>
       </c>
@@ -13316,7 +13317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>25</v>
       </c>
@@ -13360,7 +13361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>189</v>
       </c>
@@ -13407,7 +13408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>189</v>
       </c>
@@ -13454,7 +13455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>44</v>
       </c>
@@ -13498,7 +13499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>189</v>
       </c>
@@ -13545,7 +13546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>189</v>
       </c>
@@ -13592,7 +13593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>189</v>
       </c>
@@ -13639,7 +13640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>189</v>
       </c>
@@ -13686,7 +13687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>189</v>
       </c>
@@ -13733,7 +13734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>189</v>
       </c>
@@ -13780,7 +13781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>189</v>
       </c>
@@ -13827,7 +13828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -13868,7 +13869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>189</v>
       </c>
@@ -13915,7 +13916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>189</v>
       </c>
@@ -13962,7 +13963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>44</v>
       </c>
@@ -14006,7 +14007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>332</v>
       </c>
@@ -14032,7 +14033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>25</v>
       </c>
@@ -14073,7 +14074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>25</v>
       </c>
@@ -14114,7 +14115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>44</v>
       </c>
@@ -14158,7 +14159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>16</v>
       </c>
@@ -14199,7 +14200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>44</v>
       </c>
@@ -14243,7 +14244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>44</v>
       </c>
@@ -14287,7 +14288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>221</v>
       </c>
@@ -14331,7 +14332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>16</v>
       </c>
@@ -14375,7 +14376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>190</v>
       </c>
@@ -14416,7 +14417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>189</v>
       </c>
@@ -14463,7 +14464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>25</v>
       </c>
@@ -14507,7 +14508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>25</v>
       </c>
@@ -14551,7 +14552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>25</v>
       </c>
@@ -14595,7 +14596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>25</v>
       </c>
@@ -14639,7 +14640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>25</v>
       </c>
@@ -14683,7 +14684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>25</v>
       </c>
@@ -14727,7 +14728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>21</v>
       </c>
@@ -14768,7 +14769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>189</v>
       </c>
@@ -14815,7 +14816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>189</v>
       </c>
@@ -14862,7 +14863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>21</v>
       </c>
@@ -14906,7 +14907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>21</v>
       </c>
@@ -14950,7 +14951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>44</v>
       </c>
@@ -14994,7 +14995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>18</v>
       </c>
@@ -15038,7 +15039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>25</v>
       </c>
@@ -15082,7 +15083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>25</v>
       </c>
@@ -15126,7 +15127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>25</v>
       </c>
@@ -15170,7 +15171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>18</v>
       </c>
@@ -15214,7 +15215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>44</v>
       </c>
@@ -15258,7 +15259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>44</v>
       </c>
@@ -15302,7 +15303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>44</v>
       </c>
@@ -15346,7 +15347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>189</v>
       </c>
@@ -15393,7 +15394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>44</v>
       </c>
@@ -15437,7 +15438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>189</v>
       </c>
@@ -15484,7 +15485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>190</v>
       </c>
@@ -15495,13 +15496,13 @@
         <v>263</v>
       </c>
       <c r="D325">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E325">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="F325">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="G325" t="s">
         <v>272</v>
@@ -15528,7 +15529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>332</v>
       </c>
@@ -15554,7 +15555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>44</v>
       </c>
@@ -15598,7 +15599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>44</v>
       </c>
@@ -15642,7 +15643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>221</v>
       </c>
@@ -15686,7 +15687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>44</v>
       </c>
@@ -15730,7 +15731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>189</v>
       </c>
@@ -15777,7 +15778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>189</v>
       </c>
@@ -15824,7 +15825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>189</v>
       </c>
@@ -15871,7 +15872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>189</v>
       </c>
@@ -15918,7 +15919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>44</v>
       </c>
@@ -15962,7 +15963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>189</v>
       </c>
@@ -16009,7 +16010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>44</v>
       </c>
@@ -16053,7 +16054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>44</v>
       </c>
@@ -16097,7 +16098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>44</v>
       </c>
@@ -16141,7 +16142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>189</v>
       </c>
@@ -16188,7 +16189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>189</v>
       </c>
@@ -16235,7 +16236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>189</v>
       </c>
@@ -16282,7 +16283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>189</v>
       </c>
@@ -16329,7 +16330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>221</v>
       </c>
@@ -16373,7 +16374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>44</v>
       </c>
@@ -16417,7 +16418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>43</v>
       </c>
@@ -16458,7 +16459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>16</v>
       </c>
@@ -16499,7 +16500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>189</v>
       </c>
@@ -16534,7 +16535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>221</v>
       </c>
@@ -16578,7 +16579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>25</v>
       </c>
@@ -16619,7 +16620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>25</v>
       </c>
@@ -16660,7 +16661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>25</v>
       </c>
@@ -16701,7 +16702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>189</v>
       </c>
@@ -16748,7 +16749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>189</v>
       </c>
@@ -16795,7 +16796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>189</v>
       </c>
@@ -16842,7 +16843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>189</v>
       </c>
@@ -16889,7 +16890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>189</v>
       </c>
@@ -16936,7 +16937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>221</v>
       </c>
@@ -16982,6 +16983,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O358">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="kwartelkoning"/>
+      </filters>
+    </filterColumn>
     <sortState ref="A2:O358">
       <sortCondition ref="B1:B358"/>
     </sortState>

--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="11496" windowHeight="7800"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11496" windowHeight="7800"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -962,66 +962,15 @@
     <t>geleluzernevlinder</t>
   </si>
   <si>
-    <t>Baardvleermuis</t>
-  </si>
-  <si>
-    <t>Beekprik</t>
-  </si>
-  <si>
     <t>Bosvleermuis</t>
   </si>
   <si>
-    <t>Brandts vleermuis</t>
-  </si>
-  <si>
-    <t>Franjestaart</t>
-  </si>
-  <si>
-    <t>Gewone dwergvleermuis</t>
-  </si>
-  <si>
-    <t>Gewone grootoorvleermuis</t>
-  </si>
-  <si>
-    <t>Grijze grootoorvleermuis</t>
-  </si>
-  <si>
-    <t>Grote hoefijzerneus</t>
-  </si>
-  <si>
-    <t>Ingekorven vleermuis</t>
-  </si>
-  <si>
-    <t>Klein tasjeskruid</t>
-  </si>
-  <si>
     <t>Kleine dwergvleermuis</t>
   </si>
   <si>
     <t>Kleine modderkruiper</t>
   </si>
   <si>
-    <t>Laatvlieger</t>
-  </si>
-  <si>
-    <t>Meervleermuis</t>
-  </si>
-  <si>
-    <t>Rivierdonderpad</t>
-  </si>
-  <si>
-    <t>Rosse vleermuis</t>
-  </si>
-  <si>
-    <t>Ruige dwergvleermuis</t>
-  </si>
-  <si>
-    <t>Serpeling</t>
-  </si>
-  <si>
-    <t>Vale vleermuis</t>
-  </si>
-  <si>
     <t>Watervleermuis</t>
   </si>
   <si>
@@ -1077,6 +1026,57 @@
   </si>
   <si>
     <t>Voerstreek</t>
+  </si>
+  <si>
+    <t>baardvleermuis</t>
+  </si>
+  <si>
+    <t>beekprik</t>
+  </si>
+  <si>
+    <t>brandtsvleermuis</t>
+  </si>
+  <si>
+    <t>franjestaart</t>
+  </si>
+  <si>
+    <t>gewonedwergvleermuis</t>
+  </si>
+  <si>
+    <t>gewonegrootoorvleermuis</t>
+  </si>
+  <si>
+    <t>grijzegrootoorvleermuis</t>
+  </si>
+  <si>
+    <t>valevleermuis</t>
+  </si>
+  <si>
+    <t>rivierdonderpad</t>
+  </si>
+  <si>
+    <t>rossevleermuis</t>
+  </si>
+  <si>
+    <t>ruigedwergvleermuis</t>
+  </si>
+  <si>
+    <t>serpeling</t>
+  </si>
+  <si>
+    <t>meervleermuis</t>
+  </si>
+  <si>
+    <t>laatvlieger</t>
+  </si>
+  <si>
+    <t>kleintasjeskruid</t>
+  </si>
+  <si>
+    <t>ingekorvenvleermuis</t>
+  </si>
+  <si>
+    <t>grotehoefijzerneus</t>
   </si>
 </sst>
 </file>
@@ -1441,25 +1441,25 @@
         <v>287</v>
       </c>
       <c r="I1" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="J1" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="K1" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="L1" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="M1" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="N1" t="s">
         <v>309</v>
       </c>
       <c r="O1" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
@@ -1599,13 +1599,13 @@
         <v>262</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G5" t="s">
         <v>272</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B9" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1795,7 +1795,7 @@
         <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2018,7 +2018,7 @@
         <v>290</v>
       </c>
       <c r="I15" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>288</v>
       </c>
       <c r="I17" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2156,7 +2156,7 @@
         <v>288</v>
       </c>
       <c r="I18" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2182,7 +2182,7 @@
         <v>189</v>
       </c>
       <c r="B19" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C19" t="s">
         <v>262</v>
@@ -2191,7 +2191,7 @@
         <v>5000</v>
       </c>
       <c r="I19" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2217,7 +2217,7 @@
         <v>189</v>
       </c>
       <c r="B20" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C20" t="s">
         <v>262</v>
@@ -2226,7 +2226,7 @@
         <v>250000</v>
       </c>
       <c r="I20" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>288</v>
       </c>
       <c r="I28" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -2672,7 +2672,7 @@
         <v>289</v>
       </c>
       <c r="I30" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>289</v>
       </c>
       <c r="I31" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B35" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         <v>290</v>
       </c>
       <c r="I41" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -3173,7 +3173,7 @@
         <v>290</v>
       </c>
       <c r="I42" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -3874,7 +3874,7 @@
         <v>289</v>
       </c>
       <c r="I58" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -4053,7 +4053,7 @@
         <v>290</v>
       </c>
       <c r="I62" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -4100,7 +4100,7 @@
         <v>290</v>
       </c>
       <c r="I63" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -4214,7 +4214,7 @@
         <v>44</v>
       </c>
       <c r="B66" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="C66" t="s">
         <v>262</v>
@@ -4578,7 +4578,7 @@
         <v>289</v>
       </c>
       <c r="I74" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4601,10 +4601,10 @@
     </row>
     <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B75" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4780,7 +4780,7 @@
         <v>290</v>
       </c>
       <c r="I79" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>290</v>
       </c>
       <c r="I80" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4918,7 +4918,7 @@
         <v>288</v>
       </c>
       <c r="I82" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -4944,7 +4944,7 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="C83" t="s">
         <v>262</v>
@@ -5097,7 +5097,7 @@
         <v>290</v>
       </c>
       <c r="I86" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -5378,10 +5378,10 @@
     </row>
     <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B93" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="J93">
         <v>1</v>
@@ -5404,10 +5404,10 @@
     </row>
     <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B94" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>20</v>
       </c>
       <c r="E98">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F98">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G98" t="s">
         <v>272</v>
@@ -5850,7 +5850,7 @@
         <v>290</v>
       </c>
       <c r="I104" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -5897,7 +5897,7 @@
         <v>288</v>
       </c>
       <c r="I105" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -5944,7 +5944,7 @@
         <v>290</v>
       </c>
       <c r="I106" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -5991,7 +5991,7 @@
         <v>290</v>
       </c>
       <c r="I107" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -6038,7 +6038,7 @@
         <v>290</v>
       </c>
       <c r="I108" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -6085,7 +6085,7 @@
         <v>290</v>
       </c>
       <c r="I109" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>290</v>
       </c>
       <c r="I110" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -6179,7 +6179,7 @@
         <v>290</v>
       </c>
       <c r="I111" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -6226,7 +6226,7 @@
         <v>290</v>
       </c>
       <c r="I112" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -6249,10 +6249,10 @@
     </row>
     <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B113" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -6363,10 +6363,10 @@
     </row>
     <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B116" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6545,7 +6545,7 @@
         <v>290</v>
       </c>
       <c r="I120" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6592,7 +6592,7 @@
         <v>290</v>
       </c>
       <c r="I121" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -6727,7 +6727,7 @@
         <v>290</v>
       </c>
       <c r="I124" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J124">
         <v>1</v>
@@ -6774,7 +6774,7 @@
         <v>290</v>
       </c>
       <c r="I125" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -6821,7 +6821,7 @@
         <v>290</v>
       </c>
       <c r="I126" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -6847,7 +6847,7 @@
         <v>44</v>
       </c>
       <c r="B127" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="C127" t="s">
         <v>262</v>
@@ -6997,7 +6997,7 @@
         <v>290</v>
       </c>
       <c r="I130" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -7044,7 +7044,7 @@
         <v>290</v>
       </c>
       <c r="I131" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -7707,7 +7707,7 @@
         <v>289</v>
       </c>
       <c r="I146" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -7795,7 +7795,7 @@
         <v>290</v>
       </c>
       <c r="I148" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J148">
         <v>1</v>
@@ -7818,10 +7818,10 @@
     </row>
     <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B149" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="J149">
         <v>0</v>
@@ -7935,7 +7935,7 @@
         <v>44</v>
       </c>
       <c r="B152" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="C152" t="s">
         <v>262</v>
@@ -8132,7 +8132,7 @@
         <v>290</v>
       </c>
       <c r="I156" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J156">
         <v>0</v>
@@ -8246,7 +8246,7 @@
         <v>44</v>
       </c>
       <c r="B159" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="C159" t="s">
         <v>262</v>
@@ -8331,10 +8331,10 @@
     </row>
     <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B161" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="J161">
         <v>1</v>
@@ -8360,7 +8360,7 @@
         <v>41</v>
       </c>
       <c r="B162" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="J162">
         <v>0</v>
@@ -8539,7 +8539,7 @@
         <v>290</v>
       </c>
       <c r="I166" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J166">
         <v>0</v>
@@ -8674,7 +8674,7 @@
         <v>290</v>
       </c>
       <c r="I169" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>290</v>
       </c>
       <c r="I170" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J170">
         <v>0</v>
@@ -8768,7 +8768,7 @@
         <v>290</v>
       </c>
       <c r="I171" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J171">
         <v>0</v>
@@ -8947,7 +8947,7 @@
         <v>289</v>
       </c>
       <c r="I175" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J175">
         <v>0</v>
@@ -8994,7 +8994,7 @@
         <v>289</v>
       </c>
       <c r="I176" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J176">
         <v>0</v>
@@ -9173,7 +9173,7 @@
         <v>290</v>
       </c>
       <c r="I180" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J180">
         <v>0</v>
@@ -9352,7 +9352,7 @@
         <v>289</v>
       </c>
       <c r="I184" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J184">
         <v>0</v>
@@ -9399,7 +9399,7 @@
         <v>289</v>
       </c>
       <c r="I185" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J185">
         <v>0</v>
@@ -9490,7 +9490,7 @@
         <v>290</v>
       </c>
       <c r="I187" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J187">
         <v>1</v>
@@ -9625,7 +9625,7 @@
         <v>290</v>
       </c>
       <c r="I190" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J190">
         <v>0</v>
@@ -9672,7 +9672,7 @@
         <v>288</v>
       </c>
       <c r="I191" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J191">
         <v>0</v>
@@ -9719,7 +9719,7 @@
         <v>289</v>
       </c>
       <c r="I192" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J192">
         <v>1</v>
@@ -9766,7 +9766,7 @@
         <v>289</v>
       </c>
       <c r="I193" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J193">
         <v>1</v>
@@ -9787,7 +9787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>189</v>
       </c>
@@ -9813,7 +9813,7 @@
         <v>290</v>
       </c>
       <c r="I194" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J194">
         <v>0</v>
@@ -9880,10 +9880,10 @@
     </row>
     <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B196" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="J196">
         <v>1</v>
@@ -10062,7 +10062,7 @@
         <v>290</v>
       </c>
       <c r="I200" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -10109,7 +10109,7 @@
         <v>290</v>
       </c>
       <c r="I201" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -10141,13 +10141,13 @@
         <v>269</v>
       </c>
       <c r="D202">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E202">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F202">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="G202" t="s">
         <v>308</v>
@@ -10508,7 +10508,7 @@
         <v>289</v>
       </c>
       <c r="I210" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J210">
         <v>1</v>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B211" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="J211">
         <v>0</v>
@@ -10581,7 +10581,7 @@
         <v>290</v>
       </c>
       <c r="I212" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J212">
         <v>0</v>
@@ -10757,7 +10757,7 @@
         <v>288</v>
       </c>
       <c r="I216" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J216">
         <v>1</v>
@@ -10804,7 +10804,7 @@
         <v>288</v>
       </c>
       <c r="I217" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J217">
         <v>0</v>
@@ -10851,7 +10851,7 @@
         <v>288</v>
       </c>
       <c r="I218" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J218">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>289</v>
       </c>
       <c r="I228" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J228">
         <v>0</v>
@@ -11326,7 +11326,7 @@
         <v>290</v>
       </c>
       <c r="I229" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J229">
         <v>0</v>
@@ -11417,7 +11417,7 @@
         <v>290</v>
       </c>
       <c r="I231" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J231">
         <v>0</v>
@@ -11710,7 +11710,7 @@
         <v>269</v>
       </c>
       <c r="D238">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E238">
         <v>50</v>
@@ -11725,7 +11725,7 @@
         <v>290</v>
       </c>
       <c r="I238" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J238">
         <v>0</v>
@@ -11816,7 +11816,7 @@
         <v>289</v>
       </c>
       <c r="I240" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J240">
         <v>0</v>
@@ -11863,7 +11863,7 @@
         <v>289</v>
       </c>
       <c r="I241" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J241">
         <v>0</v>
@@ -11951,7 +11951,7 @@
         <v>289</v>
       </c>
       <c r="I243" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J243">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>290</v>
       </c>
       <c r="I244" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J244">
         <v>0</v>
@@ -12045,7 +12045,7 @@
         <v>290</v>
       </c>
       <c r="I245" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J245">
         <v>0</v>
@@ -12092,7 +12092,7 @@
         <v>290</v>
       </c>
       <c r="I246" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J246">
         <v>0</v>
@@ -12118,7 +12118,7 @@
         <v>41</v>
       </c>
       <c r="B247" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="J247">
         <v>0</v>
@@ -12291,7 +12291,7 @@
         <v>290</v>
       </c>
       <c r="I251" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J251">
         <v>1</v>
@@ -12338,7 +12338,7 @@
         <v>290</v>
       </c>
       <c r="I252" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J252">
         <v>1</v>
@@ -12508,7 +12508,7 @@
         <v>290</v>
       </c>
       <c r="I256" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -12555,7 +12555,7 @@
         <v>290</v>
       </c>
       <c r="I257" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J257">
         <v>0</v>
@@ -12578,10 +12578,10 @@
     </row>
     <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B258" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J258">
         <v>1</v>
@@ -12689,10 +12689,10 @@
     </row>
     <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B261" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="J261">
         <v>1</v>
@@ -12850,7 +12850,7 @@
         <v>41</v>
       </c>
       <c r="B265" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="J265">
         <v>0</v>
@@ -13029,7 +13029,7 @@
         <v>290</v>
       </c>
       <c r="I269" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J269">
         <v>0</v>
@@ -13076,7 +13076,7 @@
         <v>290</v>
       </c>
       <c r="I270" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J270">
         <v>0</v>
@@ -13146,7 +13146,7 @@
         <v>44</v>
       </c>
       <c r="B272" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="C272" t="s">
         <v>262</v>
@@ -13387,7 +13387,7 @@
         <v>290</v>
       </c>
       <c r="I277" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J277">
         <v>0</v>
@@ -13434,7 +13434,7 @@
         <v>290</v>
       </c>
       <c r="I278" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J278">
         <v>0</v>
@@ -13525,7 +13525,7 @@
         <v>289</v>
       </c>
       <c r="I280" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J280">
         <v>0</v>
@@ -13572,7 +13572,7 @@
         <v>289</v>
       </c>
       <c r="I281" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J281">
         <v>0</v>
@@ -13619,7 +13619,7 @@
         <v>289</v>
       </c>
       <c r="I282" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J282">
         <v>0</v>
@@ -13666,7 +13666,7 @@
         <v>289</v>
       </c>
       <c r="I283" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J283">
         <v>0</v>
@@ -13713,7 +13713,7 @@
         <v>290</v>
       </c>
       <c r="I284" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J284">
         <v>0</v>
@@ -13760,7 +13760,7 @@
         <v>290</v>
       </c>
       <c r="I285" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J285">
         <v>0</v>
@@ -13807,7 +13807,7 @@
         <v>288</v>
       </c>
       <c r="I286" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J286">
         <v>1</v>
@@ -13895,7 +13895,7 @@
         <v>288</v>
       </c>
       <c r="I288" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J288">
         <v>0</v>
@@ -13942,7 +13942,7 @@
         <v>288</v>
       </c>
       <c r="I289" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J289">
         <v>0</v>
@@ -14009,10 +14009,10 @@
     </row>
     <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B291" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="J291">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>189</v>
       </c>
       <c r="B301" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="C301" t="s">
         <v>273</v>
@@ -14443,7 +14443,7 @@
         <v>290</v>
       </c>
       <c r="I301" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J301">
         <v>0</v>
@@ -14795,7 +14795,7 @@
         <v>290</v>
       </c>
       <c r="I309" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -14842,7 +14842,7 @@
         <v>290</v>
       </c>
       <c r="I310" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J310">
         <v>0</v>
@@ -15373,7 +15373,7 @@
         <v>288</v>
       </c>
       <c r="I322" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J322">
         <v>0</v>
@@ -15464,7 +15464,7 @@
         <v>290</v>
       </c>
       <c r="I324" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J324">
         <v>1</v>
@@ -15531,10 +15531,10 @@
     </row>
     <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B326" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="J326">
         <v>1</v>
@@ -15757,7 +15757,7 @@
         <v>290</v>
       </c>
       <c r="I331" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J331">
         <v>0</v>
@@ -15804,7 +15804,7 @@
         <v>290</v>
       </c>
       <c r="I332" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J332">
         <v>0</v>
@@ -15851,7 +15851,7 @@
         <v>290</v>
       </c>
       <c r="I333" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J333">
         <v>0</v>
@@ -15898,7 +15898,7 @@
         <v>289</v>
       </c>
       <c r="I334" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J334">
         <v>1</v>
@@ -15989,7 +15989,7 @@
         <v>290</v>
       </c>
       <c r="I336" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J336">
         <v>0</v>
@@ -16168,7 +16168,7 @@
         <v>289</v>
       </c>
       <c r="I340" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J340">
         <v>1</v>
@@ -16215,7 +16215,7 @@
         <v>289</v>
       </c>
       <c r="I341" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J341">
         <v>1</v>
@@ -16262,7 +16262,7 @@
         <v>290</v>
       </c>
       <c r="I342" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J342">
         <v>0</v>
@@ -16309,7 +16309,7 @@
         <v>290</v>
       </c>
       <c r="I343" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="J343">
         <v>0</v>
@@ -16505,7 +16505,7 @@
         <v>189</v>
       </c>
       <c r="B348" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="C348" t="s">
         <v>262</v>
@@ -16514,7 +16514,7 @@
         <v>10000</v>
       </c>
       <c r="I348" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J348">
         <v>0</v>
@@ -16584,7 +16584,7 @@
         <v>25</v>
       </c>
       <c r="B350" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="C350" t="s">
         <v>264</v>
@@ -16625,7 +16625,7 @@
         <v>25</v>
       </c>
       <c r="B351" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="C351" t="s">
         <v>265</v>
@@ -16666,7 +16666,7 @@
         <v>25</v>
       </c>
       <c r="B352" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="C352" t="s">
         <v>266</v>
@@ -16728,7 +16728,7 @@
         <v>290</v>
       </c>
       <c r="I353" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J353">
         <v>1</v>
@@ -16775,7 +16775,7 @@
         <v>290</v>
       </c>
       <c r="I354" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J354">
         <v>1</v>
@@ -16822,7 +16822,7 @@
         <v>290</v>
       </c>
       <c r="I355" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J355">
         <v>0</v>
@@ -16869,7 +16869,7 @@
         <v>289</v>
       </c>
       <c r="I356" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J356">
         <v>0</v>
@@ -16916,7 +16916,7 @@
         <v>289</v>
       </c>
       <c r="I357" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="J357">
         <v>0</v>
@@ -16985,7 +16985,7 @@
   <autoFilter ref="A1:O358">
     <filterColumn colId="1">
       <filters>
-        <filter val="kwartelkoning"/>
+        <filter val="levendbarendehagedis"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:O358">

--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -2525,10 +2525,10 @@
         <v>5</v>
       </c>
       <c r="E27">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="G27" t="s">
         <v>272</v>
@@ -5560,7 +5560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -7167,10 +7167,10 @@
         <v>5</v>
       </c>
       <c r="E134">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F134">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="G134" t="s">
         <v>308</v>
@@ -7285,7 +7285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -7296,13 +7296,13 @@
         <v>263</v>
       </c>
       <c r="D137">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E137">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F137">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G137" t="s">
         <v>272</v>
@@ -7842,7 +7842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -7853,10 +7853,10 @@
         <v>264</v>
       </c>
       <c r="D150">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="E150">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F150">
         <v>1000</v>
@@ -7886,7 +7886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -7897,10 +7897,10 @@
         <v>269</v>
       </c>
       <c r="D151">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E151">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F151">
         <v>1000</v>
@@ -9015,7 +9015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -9026,10 +9026,10 @@
         <v>264</v>
       </c>
       <c r="D177">
-        <v>0.4</v>
+        <v>0.03</v>
       </c>
       <c r="E177">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F177">
         <v>1000</v>
@@ -9059,7 +9059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -9070,10 +9070,10 @@
         <v>263</v>
       </c>
       <c r="D178">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E178">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F178">
         <v>1000</v>
@@ -11567,7 +11567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -11578,13 +11578,13 @@
         <v>264</v>
       </c>
       <c r="D235">
-        <v>0.4</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="E235">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F235">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="G235" t="s">
         <v>272</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -11625,10 +11625,10 @@
         <v>10</v>
       </c>
       <c r="E236">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F236">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="G236" t="s">
         <v>272</v>
@@ -12602,7 +12602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>18</v>
       </c>
@@ -12613,10 +12613,13 @@
         <v>264</v>
       </c>
       <c r="D259">
-        <v>0.04</v>
+        <v>0.01</v>
+      </c>
+      <c r="E259">
+        <v>0</v>
       </c>
       <c r="F259">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="G259" t="s">
         <v>272</v>
@@ -12643,7 +12646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>18</v>
       </c>
@@ -12657,10 +12660,10 @@
         <v>10</v>
       </c>
       <c r="E260">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F260">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="G260" t="s">
         <v>272</v>
@@ -14995,7 +14998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>18</v>
       </c>
@@ -15009,10 +15012,10 @@
         <v>5</v>
       </c>
       <c r="E314">
+        <v>0</v>
+      </c>
+      <c r="F314">
         <v>500</v>
-      </c>
-      <c r="F314">
-        <v>1000</v>
       </c>
       <c r="G314" t="s">
         <v>272</v>
@@ -15171,7 +15174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>18</v>
       </c>
@@ -15182,13 +15185,13 @@
         <v>269</v>
       </c>
       <c r="D318">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E318">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F318">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="G318" t="s">
         <v>272</v>
@@ -16983,9 +16986,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O358">
-    <filterColumn colId="1">
+    <filterColumn colId="0">
       <filters>
-        <filter val="levendbarendehagedis"/>
+        <filter val="AmfiReptie"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:O358">

--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$O$358</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$O$357</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="350">
   <si>
     <t>Soort</t>
   </si>
@@ -1395,7 +1395,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:O358"/>
+  <dimension ref="A1:O357"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2190,6 +2190,9 @@
       <c r="F19">
         <v>5000</v>
       </c>
+      <c r="G19" t="s">
+        <v>272</v>
+      </c>
       <c r="I19" t="s">
         <v>327</v>
       </c>
@@ -2222,8 +2225,14 @@
       <c r="C20" t="s">
         <v>262</v>
       </c>
+      <c r="D20">
+        <v>50</v>
+      </c>
       <c r="F20">
         <v>250000</v>
+      </c>
+      <c r="G20" t="s">
+        <v>272</v>
       </c>
       <c r="I20" t="s">
         <v>326</v>
@@ -2511,7 +2520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -5560,7 +5569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -7153,7 +7162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -7285,7 +7294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -7842,7 +7851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -7886,7 +7895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -9015,7 +9024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -9059,7 +9068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -9475,10 +9484,10 @@
         <v>270</v>
       </c>
       <c r="D187">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E187">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F187">
         <v>250000</v>
@@ -9610,7 +9619,7 @@
         <v>270</v>
       </c>
       <c r="D190">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E190">
         <v>50</v>
@@ -10130,7 +10139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -11567,7 +11576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -11611,7 +11620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -12602,7 +12611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>18</v>
       </c>
@@ -12646,7 +12655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>18</v>
       </c>
@@ -13064,7 +13073,7 @@
         <v>269</v>
       </c>
       <c r="D270">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E270">
         <v>50</v>
@@ -13698,10 +13707,10 @@
         <v>178</v>
       </c>
       <c r="C284" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D284">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E284">
         <v>50</v>
@@ -13742,40 +13751,40 @@
         <v>189</v>
       </c>
       <c r="B285" t="s">
-        <v>178</v>
+        <v>252</v>
       </c>
       <c r="C285" t="s">
         <v>269</v>
       </c>
       <c r="D285">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E285">
         <v>50</v>
       </c>
       <c r="F285">
-        <v>250000</v>
+        <v>5000</v>
       </c>
       <c r="G285" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="H285" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I285" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K285">
         <v>0</v>
       </c>
       <c r="L285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N285">
         <v>1</v>
@@ -13786,22 +13795,19 @@
     </row>
     <row r="286" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>189</v>
+        <v>16</v>
       </c>
       <c r="B286" t="s">
-        <v>252</v>
+        <v>4</v>
       </c>
       <c r="C286" t="s">
         <v>269</v>
       </c>
       <c r="D286">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E286">
-        <v>50</v>
-      </c>
-      <c r="F286">
-        <v>5000</v>
+        <v>20</v>
       </c>
       <c r="G286" t="s">
         <v>308</v>
@@ -13809,23 +13815,20 @@
       <c r="H286" t="s">
         <v>288</v>
       </c>
-      <c r="I286" t="s">
-        <v>327</v>
-      </c>
       <c r="J286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K286">
         <v>0</v>
       </c>
       <c r="L286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O286">
         <v>0</v>
@@ -13833,25 +13836,31 @@
     </row>
     <row r="287" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>16</v>
+        <v>189</v>
       </c>
       <c r="B287" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="C287" t="s">
         <v>269</v>
       </c>
       <c r="D287">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E287">
-        <v>20</v>
+        <v>50</v>
+      </c>
+      <c r="F287">
+        <v>10000</v>
       </c>
       <c r="G287" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H287" t="s">
         <v>288</v>
+      </c>
+      <c r="I287" t="s">
+        <v>327</v>
       </c>
       <c r="J287">
         <v>0</v>
@@ -13880,10 +13889,10 @@
         <v>179</v>
       </c>
       <c r="C288" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="D288">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E288">
         <v>50</v>
@@ -13921,31 +13930,28 @@
     </row>
     <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="B289" t="s">
-        <v>179</v>
+        <v>111</v>
       </c>
       <c r="C289" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="D289">
-        <v>5</v>
+        <v>0.16</v>
       </c>
       <c r="E289">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F289">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G289" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="H289" t="s">
-        <v>288</v>
-      </c>
-      <c r="I289" t="s">
-        <v>327</v>
+        <v>289</v>
       </c>
       <c r="J289">
         <v>0</v>
@@ -13960,7 +13966,7 @@
         <v>0</v>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O289">
         <v>0</v>
@@ -13968,28 +13974,10 @@
     </row>
     <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>44</v>
+        <v>315</v>
       </c>
       <c r="B290" t="s">
-        <v>111</v>
-      </c>
-      <c r="C290" t="s">
-        <v>262</v>
-      </c>
-      <c r="D290">
-        <v>0.16</v>
-      </c>
-      <c r="E290">
-        <v>20</v>
-      </c>
-      <c r="F290">
-        <v>100</v>
-      </c>
-      <c r="G290" t="s">
-        <v>308</v>
-      </c>
-      <c r="H290" t="s">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="J290">
         <v>0</v>
@@ -14004,18 +13992,33 @@
         <v>0</v>
       </c>
       <c r="N290">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O290">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>315</v>
+        <v>25</v>
       </c>
       <c r="B291" t="s">
-        <v>340</v>
+        <v>30</v>
+      </c>
+      <c r="C291" t="s">
+        <v>264</v>
+      </c>
+      <c r="D291">
+        <v>0.04</v>
+      </c>
+      <c r="E291">
+        <v>50</v>
+      </c>
+      <c r="G291" t="s">
+        <v>272</v>
+      </c>
+      <c r="H291" t="s">
+        <v>290</v>
       </c>
       <c r="J291">
         <v>0</v>
@@ -14033,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="O291">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
@@ -14044,10 +14047,10 @@
         <v>30</v>
       </c>
       <c r="C292" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D292">
-        <v>0.04</v>
+        <v>5</v>
       </c>
       <c r="E292">
         <v>50</v>
@@ -14079,25 +14082,28 @@
     </row>
     <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B293" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="C293" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D293">
-        <v>5</v>
+        <v>0.16</v>
       </c>
       <c r="E293">
-        <v>50</v>
+        <v>20</v>
+      </c>
+      <c r="F293">
+        <v>100</v>
       </c>
       <c r="G293" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="H293" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J293">
         <v>0</v>
@@ -14120,28 +14126,25 @@
     </row>
     <row r="294" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B294" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="C294" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D294">
-        <v>0.16</v>
+        <v>5</v>
       </c>
       <c r="E294">
-        <v>20</v>
-      </c>
-      <c r="F294">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G294" t="s">
         <v>308</v>
       </c>
       <c r="H294" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J294">
         <v>0</v>
@@ -14164,40 +14167,43 @@
     </row>
     <row r="295" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B295" t="s">
-        <v>5</v>
+        <v>113</v>
       </c>
       <c r="C295" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D295">
-        <v>5</v>
+        <v>0.16</v>
       </c>
       <c r="E295">
-        <v>50</v>
+        <v>20</v>
+      </c>
+      <c r="F295">
+        <v>100</v>
       </c>
       <c r="G295" t="s">
         <v>308</v>
       </c>
       <c r="H295" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O295">
         <v>0</v>
@@ -14208,7 +14214,7 @@
         <v>44</v>
       </c>
       <c r="B296" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C296" t="s">
         <v>262</v>
@@ -14249,34 +14255,34 @@
     </row>
     <row r="297" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>44</v>
+        <v>221</v>
       </c>
       <c r="B297" t="s">
-        <v>114</v>
+        <v>253</v>
       </c>
       <c r="C297" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D297">
-        <v>0.16</v>
+        <v>5</v>
       </c>
       <c r="E297">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F297">
-        <v>100</v>
+        <v>2500</v>
       </c>
       <c r="G297" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H297" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J297">
         <v>1</v>
       </c>
       <c r="K297">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L297">
         <v>1</v>
@@ -14288,27 +14294,27 @@
         <v>1</v>
       </c>
       <c r="O297">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>221</v>
+        <v>16</v>
       </c>
       <c r="B298" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C298" t="s">
         <v>269</v>
       </c>
       <c r="D298">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E298">
         <v>50</v>
       </c>
       <c r="F298">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="G298" t="s">
         <v>272</v>
@@ -14317,48 +14323,45 @@
         <v>290</v>
       </c>
       <c r="J298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K298">
         <v>0</v>
       </c>
       <c r="L298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O298">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="B299" t="s">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="C299" t="s">
         <v>269</v>
       </c>
       <c r="D299">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E299">
-        <v>50</v>
-      </c>
-      <c r="F299">
-        <v>5000</v>
+        <v>20</v>
       </c>
       <c r="G299" t="s">
         <v>272</v>
       </c>
       <c r="H299" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J299">
         <v>0</v>
@@ -14381,25 +14384,31 @@
     </row>
     <row r="300" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B300" t="s">
-        <v>195</v>
+        <v>321</v>
       </c>
       <c r="C300" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D300">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E300">
-        <v>20</v>
+        <v>50</v>
+      </c>
+      <c r="F300">
+        <v>50000</v>
       </c>
       <c r="G300" t="s">
         <v>272</v>
       </c>
       <c r="H300" t="s">
-        <v>289</v>
+        <v>290</v>
+      </c>
+      <c r="I300" t="s">
+        <v>327</v>
       </c>
       <c r="J300">
         <v>0</v>
@@ -14422,22 +14431,22 @@
     </row>
     <row r="301" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>189</v>
+        <v>25</v>
       </c>
       <c r="B301" t="s">
-        <v>321</v>
+        <v>216</v>
       </c>
       <c r="C301" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="D301">
-        <v>30</v>
+        <v>0.04</v>
       </c>
       <c r="E301">
         <v>50</v>
       </c>
       <c r="F301">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="G301" t="s">
         <v>272</v>
@@ -14445,23 +14454,20 @@
       <c r="H301" t="s">
         <v>290</v>
       </c>
-      <c r="I301" t="s">
-        <v>327</v>
-      </c>
       <c r="J301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O301">
         <v>0</v>
@@ -14475,10 +14481,10 @@
         <v>216</v>
       </c>
       <c r="C302" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D302">
-        <v>0.04</v>
+        <v>5</v>
       </c>
       <c r="E302">
         <v>50</v>
@@ -14519,10 +14525,10 @@
         <v>216</v>
       </c>
       <c r="C303" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D303">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E303">
         <v>50</v>
@@ -14560,19 +14566,19 @@
         <v>25</v>
       </c>
       <c r="B304" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C304" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D304">
-        <v>50</v>
+        <v>0.01</v>
       </c>
       <c r="E304">
         <v>50</v>
       </c>
       <c r="F304">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G304" t="s">
         <v>272</v>
@@ -14607,10 +14613,10 @@
         <v>217</v>
       </c>
       <c r="C305" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D305">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="E305">
         <v>50</v>
@@ -14651,10 +14657,10 @@
         <v>217</v>
       </c>
       <c r="C306" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D306">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E306">
         <v>50</v>
@@ -14689,22 +14695,19 @@
     </row>
     <row r="307" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>217</v>
+        <v>22</v>
       </c>
       <c r="C307" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D307">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E307">
         <v>50</v>
-      </c>
-      <c r="F307">
-        <v>10000</v>
       </c>
       <c r="G307" t="s">
         <v>272</v>
@@ -14713,19 +14716,19 @@
         <v>290</v>
       </c>
       <c r="J307">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K307">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L307">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M307">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N307">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O307">
         <v>0</v>
@@ -14733,25 +14736,31 @@
     </row>
     <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="B308" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="C308" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D308">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E308">
         <v>50</v>
+      </c>
+      <c r="F308">
+        <v>50000</v>
       </c>
       <c r="G308" t="s">
         <v>272</v>
       </c>
       <c r="H308" t="s">
         <v>290</v>
+      </c>
+      <c r="I308" t="s">
+        <v>327</v>
       </c>
       <c r="J308">
         <v>0</v>
@@ -14780,13 +14789,13 @@
         <v>180</v>
       </c>
       <c r="C309" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="D309">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E309">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F309">
         <v>50000</v>
@@ -14821,22 +14830,22 @@
     </row>
     <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>180</v>
+        <v>23</v>
       </c>
       <c r="C310" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="D310">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E310">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F310">
-        <v>50000</v>
+        <v>1000</v>
       </c>
       <c r="G310" t="s">
         <v>272</v>
@@ -14844,9 +14853,6 @@
       <c r="H310" t="s">
         <v>290</v>
       </c>
-      <c r="I310" t="s">
-        <v>327</v>
-      </c>
       <c r="J310">
         <v>0</v>
       </c>
@@ -14857,13 +14863,13 @@
         <v>0</v>
       </c>
       <c r="M310">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N310">
         <v>0</v>
       </c>
       <c r="O310">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
@@ -14874,10 +14880,10 @@
         <v>23</v>
       </c>
       <c r="C311" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="D311">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E311">
         <v>50</v>
@@ -14912,43 +14918,43 @@
     </row>
     <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B312" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="C312" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="D312">
-        <v>5</v>
+        <v>0.16</v>
       </c>
       <c r="E312">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F312">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G312" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="H312" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J312">
         <v>0</v>
       </c>
       <c r="K312">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L312">
         <v>0</v>
       </c>
       <c r="M312">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N312">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O312">
         <v>1</v>
@@ -14956,34 +14962,34 @@
     </row>
     <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="B313" t="s">
-        <v>115</v>
+        <v>14</v>
       </c>
       <c r="C313" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D313">
-        <v>0.16</v>
+        <v>5</v>
       </c>
       <c r="E313">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F313">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G313" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H313" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J313">
         <v>0</v>
       </c>
       <c r="K313">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L313">
         <v>0</v>
@@ -14992,30 +14998,30 @@
         <v>0</v>
       </c>
       <c r="N313">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O313">
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B314" t="s">
-        <v>14</v>
+        <v>218</v>
       </c>
       <c r="C314" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D314">
-        <v>5</v>
+        <v>0.04</v>
       </c>
       <c r="E314">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F314">
-        <v>500</v>
+        <v>50000</v>
       </c>
       <c r="G314" t="s">
         <v>272</v>
@@ -15039,7 +15045,7 @@
         <v>0</v>
       </c>
       <c r="O314">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
@@ -15050,10 +15056,10 @@
         <v>218</v>
       </c>
       <c r="C315" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D315">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E315">
         <v>50</v>
@@ -15094,10 +15100,10 @@
         <v>218</v>
       </c>
       <c r="C316" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D316">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E316">
         <v>50</v>
@@ -15132,90 +15138,90 @@
     </row>
     <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B317" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="C317" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D317">
         <v>10</v>
       </c>
       <c r="E317">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F317">
-        <v>50000</v>
+        <v>500</v>
       </c>
       <c r="G317" t="s">
         <v>272</v>
       </c>
       <c r="H317" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J317">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K317">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L317">
         <v>0</v>
       </c>
       <c r="M317">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N317">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O317">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B318" t="s">
-        <v>201</v>
+        <v>116</v>
       </c>
       <c r="C318" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D318">
-        <v>10</v>
+        <v>0.16</v>
       </c>
       <c r="E318">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F318">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G318" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="H318" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J318">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K318">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L318">
         <v>0</v>
       </c>
       <c r="M318">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N318">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O318">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
@@ -15223,7 +15229,7 @@
         <v>44</v>
       </c>
       <c r="B319" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C319" t="s">
         <v>262</v>
@@ -15244,19 +15250,19 @@
         <v>289</v>
       </c>
       <c r="J319">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K319">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L319">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M319">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N319">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O319">
         <v>0</v>
@@ -15267,7 +15273,7 @@
         <v>44</v>
       </c>
       <c r="B320" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C320" t="s">
         <v>262</v>
@@ -15291,7 +15297,7 @@
         <v>1</v>
       </c>
       <c r="K320">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L320">
         <v>1</v>
@@ -15308,43 +15314,46 @@
     </row>
     <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="B321" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="C321" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D321">
-        <v>0.16</v>
+        <v>5</v>
       </c>
       <c r="E321">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F321">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G321" t="s">
         <v>308</v>
       </c>
       <c r="H321" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="I321" t="s">
+        <v>327</v>
       </c>
       <c r="J321">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K321">
         <v>0</v>
       </c>
       <c r="L321">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M321">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N321">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O321">
         <v>0</v>
@@ -15352,46 +15361,43 @@
     </row>
     <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="B322" t="s">
-        <v>181</v>
+        <v>119</v>
       </c>
       <c r="C322" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D322">
-        <v>5</v>
+        <v>0.16</v>
       </c>
       <c r="E322">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F322">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G322" t="s">
         <v>308</v>
       </c>
       <c r="H322" t="s">
-        <v>288</v>
-      </c>
-      <c r="I322" t="s">
-        <v>327</v>
+        <v>289</v>
       </c>
       <c r="J322">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K322">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L322">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M322">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N322">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O322">
         <v>0</v>
@@ -15399,28 +15405,31 @@
     </row>
     <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="B323" t="s">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="C323" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D323">
-        <v>0.16</v>
+        <v>10</v>
       </c>
       <c r="E323">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F323">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="G323" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H323" t="s">
-        <v>289</v>
+        <v>290</v>
+      </c>
+      <c r="I323" t="s">
+        <v>327</v>
       </c>
       <c r="J323">
         <v>1</v>
@@ -15438,27 +15447,27 @@
         <v>1</v>
       </c>
       <c r="O323">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B324" t="s">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C324" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D324">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E324">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F324">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="G324" t="s">
         <v>272</v>
@@ -15466,9 +15475,6 @@
       <c r="H324" t="s">
         <v>290</v>
       </c>
-      <c r="I324" t="s">
-        <v>327</v>
-      </c>
       <c r="J324">
         <v>1</v>
       </c>
@@ -15476,7 +15482,7 @@
         <v>1</v>
       </c>
       <c r="L324">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M324">
         <v>1</v>
@@ -15490,28 +15496,10 @@
     </row>
     <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>190</v>
+        <v>315</v>
       </c>
       <c r="B325" t="s">
-        <v>255</v>
-      </c>
-      <c r="C325" t="s">
-        <v>263</v>
-      </c>
-      <c r="D325">
-        <v>25</v>
-      </c>
-      <c r="E325">
-        <v>250</v>
-      </c>
-      <c r="F325">
-        <v>1000</v>
-      </c>
-      <c r="G325" t="s">
-        <v>272</v>
-      </c>
-      <c r="H325" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="J325">
         <v>1</v>
@@ -15523,27 +15511,45 @@
         <v>0</v>
       </c>
       <c r="M325">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N325">
         <v>1</v>
       </c>
       <c r="O325">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>315</v>
+        <v>44</v>
       </c>
       <c r="B326" t="s">
-        <v>314</v>
+        <v>120</v>
+      </c>
+      <c r="C326" t="s">
+        <v>262</v>
+      </c>
+      <c r="D326">
+        <v>0.16</v>
+      </c>
+      <c r="E326">
+        <v>20</v>
+      </c>
+      <c r="F326">
+        <v>100</v>
+      </c>
+      <c r="G326" t="s">
+        <v>308</v>
+      </c>
+      <c r="H326" t="s">
+        <v>289</v>
       </c>
       <c r="J326">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K326">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L326">
         <v>0</v>
@@ -15552,7 +15558,7 @@
         <v>0</v>
       </c>
       <c r="N326">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O326">
         <v>0</v>
@@ -15563,7 +15569,7 @@
         <v>44</v>
       </c>
       <c r="B327" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C327" t="s">
         <v>262</v>
@@ -15587,92 +15593,92 @@
         <v>0</v>
       </c>
       <c r="K327">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L327">
         <v>0</v>
       </c>
       <c r="M327">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N327">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O327">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>44</v>
+        <v>221</v>
       </c>
       <c r="B328" t="s">
-        <v>121</v>
+        <v>256</v>
       </c>
       <c r="C328" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D328">
-        <v>0.16</v>
+        <v>5</v>
       </c>
       <c r="E328">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F328">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="G328" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H328" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J328">
         <v>0</v>
       </c>
       <c r="K328">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L328">
         <v>0</v>
       </c>
       <c r="M328">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N328">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O328">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>221</v>
+        <v>44</v>
       </c>
       <c r="B329" t="s">
-        <v>256</v>
+        <v>122</v>
       </c>
       <c r="C329" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D329">
-        <v>5</v>
+        <v>0.16</v>
       </c>
       <c r="E329">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F329">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="G329" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="H329" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J329">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K329">
         <v>0</v>
@@ -15681,48 +15687,51 @@
         <v>0</v>
       </c>
       <c r="M329">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N329">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O329">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="B330" t="s">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="C330" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="D330">
-        <v>0.16</v>
+        <v>50</v>
       </c>
       <c r="E330">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F330">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="G330" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H330" t="s">
-        <v>289</v>
+        <v>290</v>
+      </c>
+      <c r="I330" t="s">
+        <v>327</v>
       </c>
       <c r="J330">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K330">
         <v>0</v>
       </c>
       <c r="L330">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M330">
         <v>1</v>
@@ -15742,13 +15751,13 @@
         <v>196</v>
       </c>
       <c r="C331" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="D331">
         <v>50</v>
       </c>
       <c r="E331">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F331">
         <v>5000</v>
@@ -15789,10 +15798,10 @@
         <v>196</v>
       </c>
       <c r="C332" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="D332">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="E332">
         <v>500</v>
@@ -15833,37 +15842,37 @@
         <v>189</v>
       </c>
       <c r="B333" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C333" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D333">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="E333">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="F333">
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="G333" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="H333" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I333" t="s">
         <v>327</v>
       </c>
       <c r="J333">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K333">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L333">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M333">
         <v>1</v>
@@ -15877,22 +15886,22 @@
     </row>
     <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="B334" t="s">
-        <v>197</v>
+        <v>123</v>
       </c>
       <c r="C334" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D334">
-        <v>10</v>
+        <v>0.16</v>
       </c>
       <c r="E334">
         <v>20</v>
       </c>
       <c r="F334">
-        <v>25000</v>
+        <v>100</v>
       </c>
       <c r="G334" t="s">
         <v>308</v>
@@ -15900,52 +15909,52 @@
       <c r="H334" t="s">
         <v>289</v>
       </c>
-      <c r="I334" t="s">
-        <v>327</v>
-      </c>
       <c r="J334">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K334">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L334">
         <v>0</v>
       </c>
       <c r="M334">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N334">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O334">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="B335" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="C335" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D335">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="E335">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F335">
-        <v>100</v>
+        <v>250000</v>
       </c>
       <c r="G335" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H335" t="s">
-        <v>289</v>
+        <v>290</v>
+      </c>
+      <c r="I335" t="s">
+        <v>326</v>
       </c>
       <c r="J335">
         <v>0</v>
@@ -15960,7 +15969,7 @@
         <v>0</v>
       </c>
       <c r="N335">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O335">
         <v>0</v>
@@ -15968,43 +15977,40 @@
     </row>
     <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="B336" t="s">
-        <v>183</v>
+        <v>124</v>
       </c>
       <c r="C336" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D336">
-        <v>5</v>
+        <v>0.16</v>
       </c>
       <c r="E336">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F336">
-        <v>250000</v>
+        <v>100</v>
       </c>
       <c r="G336" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="H336" t="s">
-        <v>290</v>
-      </c>
-      <c r="I336" t="s">
-        <v>326</v>
+        <v>289</v>
       </c>
       <c r="J336">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K336">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L336">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M336">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N336">
         <v>1</v>
@@ -16018,7 +16024,7 @@
         <v>44</v>
       </c>
       <c r="B337" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C337" t="s">
         <v>262</v>
@@ -16042,7 +16048,7 @@
         <v>1</v>
       </c>
       <c r="K337">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L337">
         <v>1</v>
@@ -16062,7 +16068,7 @@
         <v>44</v>
       </c>
       <c r="B338" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C338" t="s">
         <v>262</v>
@@ -16083,19 +16089,19 @@
         <v>289</v>
       </c>
       <c r="J338">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K338">
         <v>0</v>
       </c>
       <c r="L338">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M338">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N338">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O338">
         <v>0</v>
@@ -16103,31 +16109,34 @@
     </row>
     <row r="339" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="B339" t="s">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="C339" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="D339">
-        <v>0.16</v>
+        <v>10</v>
       </c>
       <c r="E339">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F339">
-        <v>100</v>
+        <v>250000</v>
       </c>
       <c r="G339" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H339" t="s">
         <v>289</v>
       </c>
+      <c r="I339" t="s">
+        <v>327</v>
+      </c>
       <c r="J339">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K339">
         <v>0</v>
@@ -16153,13 +16162,13 @@
         <v>184</v>
       </c>
       <c r="C340" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="D340">
+        <v>1</v>
+      </c>
+      <c r="E340">
         <v>10</v>
-      </c>
-      <c r="E340">
-        <v>50</v>
       </c>
       <c r="F340">
         <v>250000</v>
@@ -16197,43 +16206,43 @@
         <v>189</v>
       </c>
       <c r="B341" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C341" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="D341">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E341">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F341">
-        <v>250000</v>
+        <v>5000</v>
       </c>
       <c r="G341" t="s">
         <v>272</v>
       </c>
       <c r="H341" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I341" t="s">
         <v>327</v>
       </c>
       <c r="J341">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K341">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L341">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M341">
         <v>0</v>
       </c>
       <c r="N341">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O341">
         <v>0</v>
@@ -16256,7 +16265,7 @@
         <v>100</v>
       </c>
       <c r="F342">
-        <v>5000</v>
+        <v>250000</v>
       </c>
       <c r="G342" t="s">
         <v>272</v>
@@ -16265,7 +16274,7 @@
         <v>290</v>
       </c>
       <c r="I342" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J342">
         <v>0</v>
@@ -16288,22 +16297,22 @@
     </row>
     <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="B343" t="s">
-        <v>185</v>
+        <v>257</v>
       </c>
       <c r="C343" t="s">
         <v>269</v>
       </c>
       <c r="D343">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="E343">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F343">
-        <v>250000</v>
+        <v>1000</v>
       </c>
       <c r="G343" t="s">
         <v>272</v>
@@ -16311,11 +16320,8 @@
       <c r="H343" t="s">
         <v>290</v>
       </c>
-      <c r="I343" t="s">
-        <v>326</v>
-      </c>
       <c r="J343">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K343">
         <v>1</v>
@@ -16324,83 +16330,80 @@
         <v>1</v>
       </c>
       <c r="M343">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N343">
         <v>1</v>
       </c>
       <c r="O343">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>221</v>
+        <v>44</v>
       </c>
       <c r="B344" t="s">
-        <v>257</v>
+        <v>127</v>
       </c>
       <c r="C344" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D344">
-        <v>5</v>
+        <v>0.16</v>
       </c>
       <c r="E344">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F344">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G344" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="H344" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O344">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B345" t="s">
-        <v>127</v>
+        <v>39</v>
       </c>
       <c r="C345" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="D345">
-        <v>0.16</v>
+        <v>0.04</v>
       </c>
       <c r="E345">
-        <v>20</v>
-      </c>
-      <c r="F345">
         <v>100</v>
       </c>
       <c r="G345" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H345" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J345">
         <v>0</v>
@@ -16423,22 +16426,22 @@
     </row>
     <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="B346" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C346" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D346">
-        <v>0.04</v>
+        <v>2</v>
       </c>
       <c r="E346">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G346" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="H346" t="s">
         <v>288</v>
@@ -16464,31 +16467,31 @@
     </row>
     <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>16</v>
+        <v>189</v>
       </c>
       <c r="B347" t="s">
-        <v>6</v>
+        <v>323</v>
       </c>
       <c r="C347" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D347">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="E347">
         <v>50</v>
       </c>
-      <c r="G347" t="s">
-        <v>308</v>
-      </c>
-      <c r="H347" t="s">
-        <v>288</v>
+      <c r="F347">
+        <v>10000</v>
+      </c>
+      <c r="I347" t="s">
+        <v>327</v>
       </c>
       <c r="J347">
         <v>0</v>
       </c>
       <c r="K347">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L347">
         <v>0</v>
@@ -16497,92 +16500,98 @@
         <v>0</v>
       </c>
       <c r="N347">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O347">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="B348" t="s">
-        <v>323</v>
+        <v>258</v>
       </c>
       <c r="C348" t="s">
-        <v>262</v>
+        <v>269</v>
+      </c>
+      <c r="D348">
+        <v>1</v>
+      </c>
+      <c r="E348">
+        <v>50</v>
       </c>
       <c r="F348">
+        <v>250</v>
+      </c>
+      <c r="G348" t="s">
+        <v>272</v>
+      </c>
+      <c r="H348" t="s">
+        <v>290</v>
+      </c>
+      <c r="J348">
+        <v>0</v>
+      </c>
+      <c r="K348">
+        <v>1</v>
+      </c>
+      <c r="L348">
+        <v>0</v>
+      </c>
+      <c r="M348">
+        <v>0</v>
+      </c>
+      <c r="N348">
+        <v>1</v>
+      </c>
+      <c r="O348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>25</v>
+      </c>
+      <c r="B349" t="s">
+        <v>322</v>
+      </c>
+      <c r="C349" t="s">
+        <v>264</v>
+      </c>
+      <c r="D349">
+        <v>0.01</v>
+      </c>
+      <c r="E349">
+        <v>50</v>
+      </c>
+      <c r="F349">
         <v>10000</v>
       </c>
-      <c r="I348" t="s">
-        <v>327</v>
-      </c>
-      <c r="J348">
-        <v>0</v>
-      </c>
-      <c r="K348">
-        <v>1</v>
-      </c>
-      <c r="L348">
-        <v>0</v>
-      </c>
-      <c r="M348">
-        <v>0</v>
-      </c>
-      <c r="N348">
-        <v>1</v>
-      </c>
-      <c r="O348">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A349" t="s">
-        <v>221</v>
-      </c>
-      <c r="B349" t="s">
-        <v>258</v>
-      </c>
-      <c r="C349" t="s">
-        <v>269</v>
-      </c>
-      <c r="D349">
-        <v>5</v>
-      </c>
-      <c r="E349">
-        <v>50</v>
-      </c>
-      <c r="F349">
-        <v>5000</v>
-      </c>
       <c r="G349" t="s">
         <v>272</v>
       </c>
-      <c r="H349" t="s">
-        <v>290</v>
-      </c>
       <c r="J349">
         <v>0</v>
       </c>
       <c r="K349">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L349">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M349">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N349">
         <v>1</v>
       </c>
       <c r="O349">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>25</v>
       </c>
@@ -16590,10 +16599,10 @@
         <v>322</v>
       </c>
       <c r="C350" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D350">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="E350">
         <v>50</v>
@@ -16623,7 +16632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>25</v>
       </c>
@@ -16631,10 +16640,10 @@
         <v>322</v>
       </c>
       <c r="C351" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D351">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E351">
         <v>50</v>
@@ -16664,30 +16673,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>25</v>
+        <v>189</v>
       </c>
       <c r="B352" t="s">
-        <v>322</v>
+        <v>186</v>
       </c>
       <c r="C352" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="D352">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="E352">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F352">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G352" t="s">
         <v>272</v>
       </c>
+      <c r="H352" t="s">
+        <v>290</v>
+      </c>
+      <c r="I352" t="s">
+        <v>327</v>
+      </c>
       <c r="J352">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K352">
         <v>0</v>
@@ -16705,7 +16720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>189</v>
       </c>
@@ -16713,10 +16728,10 @@
         <v>186</v>
       </c>
       <c r="C353" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D353">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="E353">
         <v>100</v>
@@ -16752,21 +16767,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>189</v>
       </c>
       <c r="B354" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C354" t="s">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="D354">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="E354">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F354">
         <v>5000</v>
@@ -16781,19 +16796,19 @@
         <v>327</v>
       </c>
       <c r="J354">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K354">
         <v>0</v>
       </c>
       <c r="L354">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M354">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N354">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O354">
         <v>0</v>
@@ -16804,25 +16819,25 @@
         <v>189</v>
       </c>
       <c r="B355" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C355" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="D355">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="E355">
         <v>50</v>
       </c>
       <c r="F355">
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="G355" t="s">
         <v>272</v>
       </c>
       <c r="H355" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I355" t="s">
         <v>327</v>
@@ -16840,7 +16855,7 @@
         <v>0</v>
       </c>
       <c r="N355">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O355">
         <v>0</v>
@@ -16854,10 +16869,10 @@
         <v>188</v>
       </c>
       <c r="C356" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D356">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="E356">
         <v>50</v>
@@ -16895,31 +16910,28 @@
     </row>
     <row r="357" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="B357" t="s">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="C357" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D357">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="E357">
         <v>50</v>
       </c>
       <c r="F357">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="G357" t="s">
         <v>272</v>
       </c>
       <c r="H357" t="s">
-        <v>289</v>
-      </c>
-      <c r="I357" t="s">
-        <v>327</v>
+        <v>290</v>
       </c>
       <c r="J357">
         <v>0</v>
@@ -16934,61 +16946,19 @@
         <v>0</v>
       </c>
       <c r="N357">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O357">
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A358" t="s">
-        <v>221</v>
-      </c>
-      <c r="B358" t="s">
-        <v>260</v>
-      </c>
-      <c r="C358" t="s">
-        <v>269</v>
-      </c>
-      <c r="D358">
-        <v>5</v>
-      </c>
-      <c r="E358">
-        <v>50</v>
-      </c>
-      <c r="F358">
-        <v>5000</v>
-      </c>
-      <c r="G358" t="s">
-        <v>272</v>
-      </c>
-      <c r="H358" t="s">
-        <v>290</v>
-      </c>
-      <c r="J358">
-        <v>0</v>
-      </c>
-      <c r="K358">
-        <v>0</v>
-      </c>
-      <c r="L358">
-        <v>0</v>
-      </c>
-      <c r="M358">
-        <v>0</v>
-      </c>
-      <c r="N358">
-        <v>0</v>
-      </c>
-      <c r="O358">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O358">
-    <filterColumn colId="0">
+  <autoFilter ref="A1:O357">
+    <filterColumn colId="1">
       <filters>
-        <filter val="AmfiReptie"/>
+        <filter val="zwarteheidelibel"/>
+        <filter val="zwartespecht"/>
+        <filter val="zwartestern"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:O358">
